--- a/changes/545-ammo-super.xlsx
+++ b/changes/545-ammo-super.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-balancing\changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DBE9C4D-81FB-409F-9480-9C2989A98A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFC58F3-F8D4-4233-B03C-9EFF65720DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -976,8 +976,8 @@
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="damage_torso_c" dataDxfId="4"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="damage_torso_d" dataDxfId="3"/>
     <tableColumn id="43" xr3:uid="{D5021237-E759-4A3A-B219-A4E638DB2DAD}" name="damage_arm_d" dataDxfId="2"/>
-    <tableColumn id="45" xr3:uid="{55603E35-2152-4FD3-9598-9256E449C5B0}" name="damage_leg_d" dataDxfId="0"/>
-    <tableColumn id="44" xr3:uid="{8CA87E20-CD33-48FB-A112-3BC0E2D56BD8}" name="damage_head_d" dataDxfId="1"/>
+    <tableColumn id="45" xr3:uid="{55603E35-2152-4FD3-9598-9256E449C5B0}" name="damage_leg_d" dataDxfId="1"/>
+    <tableColumn id="44" xr3:uid="{8CA87E20-CD33-48FB-A112-3BC0E2D56BD8}" name="damage_head_d" dataDxfId="0"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="damage_25"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="damage_75"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="damage_150"/>
@@ -1522,13 +1522,13 @@
       </c>
       <c r="AC3" s="3" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",AmmoChangeSheet[[#This Row],[pen_low]],";",AmmoChangeSheet[[#This Row],[pen_high]],";",AmmoChangeSheet[[#This Row],[pen_velocity_low]],";",AmmoChangeSheet[[#This Row],[pen_velocity_high]],")")</f>
-        <v>stat(bullet_velocity;0.4;1.2;1500;3000)</v>
+        <v>stat(bullet_velocity;0.25;0.75;1500;3000)</v>
       </c>
       <c r="AD3" s="11">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="AE3" s="11">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="AF3" s="15">
         <v>1500</v>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="AI3" s="13">
         <f t="shared" ref="AI3:AI12" si="0">MAX(AD3,MIN(AE3,AD3+(AH3-AF3)*(AE3-AD3)/(AG3-AF3)))</f>
-        <v>0.84960000000000002</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="AJ3" s="19">
         <v>19</v>
@@ -1568,11 +1568,11 @@
       </c>
       <c r="AP3" s="21">
         <f>(AI3-Model!$B$8)*Model!$B$38</f>
-        <v>-0.60159999999999991</v>
+        <v>-1.8759999999999999</v>
       </c>
       <c r="AQ3" s="21">
         <f t="shared" ref="AQ3:AQ12" si="1">SUM(AL3:AP3)</f>
-        <v>0.97340000000000426</v>
+        <v>-0.30099999999999572</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -1666,13 +1666,13 @@
       </c>
       <c r="AC4" s="3" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",AmmoChangeSheet[[#This Row],[pen_low]],";",AmmoChangeSheet[[#This Row],[pen_high]],";",AmmoChangeSheet[[#This Row],[pen_velocity_low]],";",AmmoChangeSheet[[#This Row],[pen_velocity_high]],")")</f>
-        <v>stat(bullet_velocity;0.3;1.1;1500;3000)</v>
+        <v>stat(bullet_velocity;0.2;0.7;1500;3000)</v>
       </c>
       <c r="AD4" s="11">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AE4" s="11">
-        <v>1.1000000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AF4" s="15">
         <v>1500</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AI4" s="13">
         <f t="shared" si="0"/>
-        <v>0.76293333333333346</v>
+        <v>0.48933333333333329</v>
       </c>
       <c r="AJ4" s="19">
         <v>22</v>
@@ -1712,11 +1712,11 @@
       </c>
       <c r="AP4" s="21">
         <f>(AI4-Model!$B$8)*Model!$B$38</f>
-        <v>-0.94826666666666615</v>
+        <v>-2.0426666666666669</v>
       </c>
       <c r="AQ4" s="21">
         <f t="shared" si="1"/>
-        <v>1.8267333333333364</v>
+        <v>0.73233333333333572</v>
       </c>
     </row>
     <row r="5" spans="1:43">
@@ -1810,13 +1810,13 @@
       </c>
       <c r="AC5" s="3" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",AmmoChangeSheet[[#This Row],[pen_low]],";",AmmoChangeSheet[[#This Row],[pen_high]],";",AmmoChangeSheet[[#This Row],[pen_velocity_low]],";",AmmoChangeSheet[[#This Row],[pen_velocity_high]],")")</f>
-        <v>stat(bullet_velocity;0.5;1.3;1500;3000)</v>
+        <v>stat(bullet_velocity;0.35;0.85;1500;3000)</v>
       </c>
       <c r="AD5" s="11">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="AE5" s="11">
-        <v>1.3</v>
+        <v>0.85</v>
       </c>
       <c r="AF5" s="15">
         <v>1500</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AI5" s="13">
         <f t="shared" si="0"/>
-        <v>0.9362666666666668</v>
+        <v>0.6226666666666667</v>
       </c>
       <c r="AJ5" s="19">
         <v>25</v>
@@ -1856,11 +1856,11 @@
       </c>
       <c r="AP5" s="21">
         <f>(AI5-Model!$B$8)*Model!$B$38</f>
-        <v>-0.25493333333333279</v>
+        <v>-1.5093333333333332</v>
       </c>
       <c r="AQ5" s="21">
         <f t="shared" si="1"/>
-        <v>1.0700666666666736</v>
+        <v>-0.1843333333333268</v>
       </c>
     </row>
     <row r="6" spans="1:43">
@@ -1954,13 +1954,13 @@
       </c>
       <c r="AC6" s="3" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",AmmoChangeSheet[[#This Row],[pen_low]],";",AmmoChangeSheet[[#This Row],[pen_high]],";",AmmoChangeSheet[[#This Row],[pen_velocity_low]],";",AmmoChangeSheet[[#This Row],[pen_velocity_high]],")")</f>
-        <v>stat(bullet_velocity;0.75;1.55;1500;3000)</v>
+        <v>stat(bullet_velocity;0.8;1.3;1500;3000)</v>
       </c>
       <c r="AD6" s="11">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AE6" s="11">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AF6" s="15">
         <v>1500</v>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AI6" s="13">
         <f t="shared" si="0"/>
-        <v>1.1862666666666668</v>
+        <v>1.0726666666666667</v>
       </c>
       <c r="AJ6" s="19">
         <v>21</v>
@@ -2000,11 +2000,11 @@
       </c>
       <c r="AP6" s="21">
         <f>(AI6-Model!$B$8)*Model!$B$38</f>
-        <v>0.74506666666666721</v>
+        <v>0.29066666666666663</v>
       </c>
       <c r="AQ6" s="21">
         <f t="shared" si="1"/>
-        <v>0.56006666666667926</v>
+        <v>0.10566666666667868</v>
       </c>
     </row>
     <row r="7" spans="1:43">
@@ -2098,13 +2098,13 @@
       </c>
       <c r="AC7" s="3" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",AmmoChangeSheet[[#This Row],[pen_low]],";",AmmoChangeSheet[[#This Row],[pen_high]],";",AmmoChangeSheet[[#This Row],[pen_velocity_low]],";",AmmoChangeSheet[[#This Row],[pen_velocity_high]],")")</f>
-        <v>stat(bullet_velocity;0.45;1.25;1500;3000)</v>
+        <v>stat(bullet_velocity;0.35;0.85;1500;3000)</v>
       </c>
       <c r="AD7" s="11">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="AE7" s="11">
-        <v>1.25</v>
+        <v>0.85</v>
       </c>
       <c r="AF7" s="15">
         <v>1500</v>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="AI7" s="13">
         <f t="shared" si="0"/>
-        <v>0.85960000000000014</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="AJ7" s="19">
         <v>20</v>
@@ -2144,11 +2144,11 @@
       </c>
       <c r="AP7" s="21">
         <f>(AI7-Model!$B$8)*Model!$B$38</f>
-        <v>-0.56159999999999943</v>
+        <v>-1.5760000000000001</v>
       </c>
       <c r="AQ7" s="21">
         <f t="shared" si="1"/>
-        <v>1.8434000000000155</v>
+        <v>0.82900000000001484</v>
       </c>
     </row>
     <row r="8" spans="1:43">
@@ -2242,13 +2242,13 @@
       </c>
       <c r="AC8" s="3" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",AmmoChangeSheet[[#This Row],[pen_low]],";",AmmoChangeSheet[[#This Row],[pen_high]],";",AmmoChangeSheet[[#This Row],[pen_velocity_low]],";",AmmoChangeSheet[[#This Row],[pen_velocity_high]],")")</f>
-        <v>stat(bullet_velocity;0.25;1.05;1500;3000)</v>
+        <v>stat(bullet_velocity;0.2;0.7;1500;3000)</v>
       </c>
       <c r="AD8" s="11">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AE8" s="11">
-        <v>1.05</v>
+        <v>0.7</v>
       </c>
       <c r="AF8" s="15">
         <v>1500</v>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AI8" s="13">
         <f t="shared" si="0"/>
-        <v>0.6862666666666668</v>
+        <v>0.47266666666666662</v>
       </c>
       <c r="AJ8" s="19">
         <v>17</v>
@@ -2288,11 +2288,11 @@
       </c>
       <c r="AP8" s="21">
         <f>(AI8-Model!$B$8)*Model!$B$38</f>
-        <v>-1.2549333333333328</v>
+        <v>-2.1093333333333337</v>
       </c>
       <c r="AQ8" s="21">
         <f t="shared" si="1"/>
-        <v>1.8700666666666712</v>
+        <v>1.0156666666666703</v>
       </c>
     </row>
     <row r="9" spans="1:43">
@@ -2386,13 +2386,13 @@
       </c>
       <c r="AC9" s="3" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",AmmoChangeSheet[[#This Row],[pen_low]],";",AmmoChangeSheet[[#This Row],[pen_high]],";",AmmoChangeSheet[[#This Row],[pen_velocity_low]],";",AmmoChangeSheet[[#This Row],[pen_velocity_high]],")")</f>
-        <v>stat(bullet_velocity;0.2;1;1500;3000)</v>
+        <v>stat(bullet_velocity;0.15;0.65;1500;3000)</v>
       </c>
       <c r="AD9" s="11">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="AE9" s="11">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="AF9" s="15">
         <v>1500</v>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="AI9" s="13">
         <f t="shared" si="0"/>
-        <v>0.59626666666666672</v>
+        <v>0.39766666666666667</v>
       </c>
       <c r="AJ9" s="19">
         <v>18</v>
@@ -2432,11 +2432,11 @@
       </c>
       <c r="AP9" s="21">
         <f>(AI9-Model!$B$8)*Model!$B$38</f>
-        <v>-1.6149333333333331</v>
+        <v>-2.4093333333333335</v>
       </c>
       <c r="AQ9" s="21">
         <f t="shared" si="1"/>
-        <v>2.3350666666666671</v>
+        <v>1.5406666666666666</v>
       </c>
     </row>
     <row r="10" spans="1:43">
@@ -2530,13 +2530,13 @@
       </c>
       <c r="AC10" s="3" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",AmmoChangeSheet[[#This Row],[pen_low]],";",AmmoChangeSheet[[#This Row],[pen_high]],";",AmmoChangeSheet[[#This Row],[pen_velocity_low]],";",AmmoChangeSheet[[#This Row],[pen_velocity_high]],")")</f>
-        <v>stat(bullet_velocity;0.6;1.4;1500;3000)</v>
+        <v>stat(bullet_velocity;0.7;1.2;1500;3000)</v>
       </c>
       <c r="AD10" s="11">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="AE10" s="11">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AF10" s="15">
         <v>1500</v>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="AI10" s="13">
         <f t="shared" si="0"/>
-        <v>0.99626666666666663</v>
+        <v>0.94766666666666666</v>
       </c>
       <c r="AJ10" s="19">
         <v>26</v>
@@ -2576,11 +2576,11 @@
       </c>
       <c r="AP10" s="21">
         <f>(AI10-Model!$B$8)*Model!$B$38</f>
-        <v>-1.4933333333333465E-2</v>
+        <v>-0.20933333333333337</v>
       </c>
       <c r="AQ10" s="21">
         <f t="shared" si="1"/>
-        <v>2.2050666666666681</v>
+        <v>2.0106666666666682</v>
       </c>
     </row>
     <row r="11" spans="1:43">
@@ -2674,13 +2674,13 @@
       </c>
       <c r="AC11" s="3" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",AmmoChangeSheet[[#This Row],[pen_low]],";",AmmoChangeSheet[[#This Row],[pen_high]],";",AmmoChangeSheet[[#This Row],[pen_velocity_low]],";",AmmoChangeSheet[[#This Row],[pen_velocity_high]],")")</f>
-        <v>stat(bullet_velocity;1;1.8;1500;3000)</v>
+        <v>stat(bullet_velocity;1.05;1.55;1500;3000)</v>
       </c>
       <c r="AD11" s="11">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AE11" s="11">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AF11" s="15">
         <v>1500</v>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AI11" s="13">
         <f t="shared" si="0"/>
-        <v>1.3962666666666665</v>
+        <v>1.2976666666666667</v>
       </c>
       <c r="AJ11" s="19">
         <v>24</v>
@@ -2720,11 +2720,11 @@
       </c>
       <c r="AP11" s="21">
         <f>(AI11-Model!$B$8)*Model!$B$38</f>
-        <v>1.5850666666666662</v>
+        <v>1.190666666666667</v>
       </c>
       <c r="AQ11" s="21">
         <f t="shared" si="1"/>
-        <v>2.2200666666666753</v>
+        <v>1.8256666666666761</v>
       </c>
     </row>
     <row r="12" spans="1:43">
@@ -2820,13 +2820,13 @@
       </c>
       <c r="AC12" s="3" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",AmmoChangeSheet[[#This Row],[pen_low]],";",AmmoChangeSheet[[#This Row],[pen_high]],";",AmmoChangeSheet[[#This Row],[pen_velocity_low]],";",AmmoChangeSheet[[#This Row],[pen_velocity_high]],")")</f>
-        <v>stat(bullet_velocity;0;0.8;500;2000)</v>
+        <v>stat(bullet_velocity;0;0.5;500;2000)</v>
       </c>
       <c r="AD12" s="12">
         <v>0</v>
       </c>
       <c r="AE12" s="12">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AF12" s="17">
         <v>500</v>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="AI12" s="14">
         <f t="shared" si="0"/>
-        <v>0.34293333333333331</v>
+        <v>0.21433333333333332</v>
       </c>
       <c r="AJ12" s="20">
         <v>23</v>
@@ -2866,11 +2866,11 @@
       </c>
       <c r="AP12" s="22">
         <f>(AI12-Model!$B$8)*Model!$B$38</f>
-        <v>-2.6282666666666668</v>
+        <v>-3.1426666666666669</v>
       </c>
       <c r="AQ12" s="22">
         <f t="shared" si="1"/>
-        <v>-4.7532666666666623</v>
+        <v>-5.2676666666666625</v>
       </c>
     </row>
   </sheetData>

--- a/changes/545-ammo-super.xlsx
+++ b/changes/545-ammo-super.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-balancing\changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFC58F3-F8D4-4233-B03C-9EFF65720DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9CEC011-75DD-4E63-AB0A-5E3113EA29EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2018,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="7">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E7" s="38">
         <v>1</v>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="AL7" s="21">
         <f>C7*Model!$B$24+D7*Model!$B$25+E7*Model!$B$26+F7*Model!$B$27+G7*Model!$B$28+H7*Model!$B$29+I7*Model!$B$30+J7*Model!$B$31+K7*Model!$B$32</f>
-        <v>-3.0750000000000002</v>
+        <v>-2.875</v>
       </c>
       <c r="AM7" s="21">
         <f>(Z7-Model!$B$5)*Model!$B$35</f>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AQ7" s="21">
         <f t="shared" si="1"/>
-        <v>0.82900000000001484</v>
+        <v>1.029000000000015</v>
       </c>
     </row>
     <row r="8" spans="1:43">
@@ -2306,7 +2306,7 @@
         <v>-1</v>
       </c>
       <c r="D9" s="7">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E9" s="38">
         <v>2</v>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="AL9" s="21">
         <f>C9*Model!$B$24+D9*Model!$B$25+E9*Model!$B$26+F9*Model!$B$27+G9*Model!$B$28+H9*Model!$B$29+I9*Model!$B$30+J9*Model!$B$31+K9*Model!$B$32</f>
-        <v>-2.5</v>
+        <v>-2.3000000000000003</v>
       </c>
       <c r="AM9" s="21">
         <f>(Z9-Model!$B$5)*Model!$B$35</f>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="AQ9" s="21">
         <f t="shared" si="1"/>
-        <v>1.5406666666666666</v>
+        <v>1.7406666666666659</v>
       </c>
     </row>
     <row r="10" spans="1:43">
@@ -2450,7 +2450,7 @@
         <v>-1</v>
       </c>
       <c r="D10" s="7">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="E10" s="38">
         <v>2</v>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="AL10" s="21">
         <f>C10*Model!$B$24+D10*Model!$B$25+E10*Model!$B$26+F10*Model!$B$27+G10*Model!$B$28+H10*Model!$B$29+I10*Model!$B$30+J10*Model!$B$31+K10*Model!$B$32</f>
-        <v>-4</v>
+        <v>-3.6000000000000005</v>
       </c>
       <c r="AM10" s="21">
         <f>(Z10-Model!$B$5)*Model!$B$35</f>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AQ10" s="21">
         <f t="shared" si="1"/>
-        <v>2.0106666666666682</v>
+        <v>2.4106666666666676</v>
       </c>
     </row>
     <row r="11" spans="1:43">
@@ -2594,7 +2594,7 @@
         <v>-1</v>
       </c>
       <c r="D11" s="7">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="E11" s="38">
         <v>2</v>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="AL11" s="21">
         <f>C11*Model!$B$24+D11*Model!$B$25+E11*Model!$B$26+F11*Model!$B$27+G11*Model!$B$28+H11*Model!$B$29+I11*Model!$B$30+J11*Model!$B$31+K11*Model!$B$32</f>
-        <v>-3.3000000000000003</v>
+        <v>-2.9000000000000004</v>
       </c>
       <c r="AM11" s="21">
         <f>(Z11-Model!$B$5)*Model!$B$35</f>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="AQ11" s="21">
         <f t="shared" si="1"/>
-        <v>1.8256666666666761</v>
+        <v>2.225666666666676</v>
       </c>
     </row>
     <row r="12" spans="1:43">
@@ -2738,7 +2738,7 @@
         <v>3</v>
       </c>
       <c r="D12" s="8">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="E12" s="39">
         <v>-2</v>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AL12" s="22">
         <f>C12*Model!$B$24+D12*Model!$B$25+E12*Model!$B$26+F12*Model!$B$27+G12*Model!$B$28+H12*Model!$B$29+I12*Model!$B$30+J12*Model!$B$31+K12*Model!$B$32</f>
-        <v>-4.7</v>
+        <v>-4.3</v>
       </c>
       <c r="AM12" s="22">
         <f>(Z12-Model!$B$5)*Model!$B$35</f>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="AQ12" s="22">
         <f t="shared" si="1"/>
-        <v>-5.2676666666666625</v>
+        <v>-4.8676666666666621</v>
       </c>
     </row>
   </sheetData>

--- a/changes/545-ammo-super.xlsx
+++ b/changes/545-ammo-super.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-balancing\changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9CEC011-75DD-4E63-AB0A-5E3113EA29EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66AE15E-29D9-48AB-91D6-6706B5F73042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
     <author>tc={534C6D01-DEB9-6875-6EC6-551F5A30F31B}</author>
   </authors>
   <commentList>
-    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -49,7 +49,7 @@
     Direct values from calibers.csv. Edit these cells on this sheet to tune the ammo model.</t>
       </text>
     </comment>
-    <comment ref="S2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="T2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -57,7 +57,7 @@
     Damage formula: MAX(MIN(a × distance + b, c) × d, 0). Distances and weights are on the Model sheet.</t>
       </text>
     </comment>
-    <comment ref="AI2" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="AJ2" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="105">
   <si>
     <t>balancing.csv inputs</t>
   </si>
@@ -400,6 +400,9 @@
   </si>
   <si>
     <t>damage_head_d</t>
+  </si>
+  <si>
+    <t>muzzle_loudness</t>
   </si>
 </sst>
 </file>
@@ -691,7 +694,44 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF1F2933"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEAF3F8"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD8E0E7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD8E0E7"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -909,7 +949,7 @@
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -958,26 +998,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="AmmoChangeSheet" displayName="AmmoChangeSheet" ref="A2:AQ12" totalsRowShown="0">
-  <tableColumns count="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="AmmoChangeSheet" displayName="AmmoChangeSheet" ref="A2:AR12" totalsRowShown="0">
+  <tableColumns count="44">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="name"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="pretty_name"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ergonomics" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ergonomics" dataDxfId="13"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="weight"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="horizontal_recoil" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="vertical_recoil" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="horizontal_recoil" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="vertical_recoil" dataDxfId="11"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="barrel_deviation"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="bullet_damage"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="bullet_velocity" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="fire_rate" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="price" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="damage_torso_a" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="damage_torso_b" dataDxfId="5"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="damage_torso_c" dataDxfId="4"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="damage_torso_d" dataDxfId="3"/>
-    <tableColumn id="43" xr3:uid="{D5021237-E759-4A3A-B219-A4E638DB2DAD}" name="damage_arm_d" dataDxfId="2"/>
-    <tableColumn id="45" xr3:uid="{55603E35-2152-4FD3-9598-9256E449C5B0}" name="damage_leg_d" dataDxfId="1"/>
-    <tableColumn id="44" xr3:uid="{8CA87E20-CD33-48FB-A112-3BC0E2D56BD8}" name="damage_head_d" dataDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="bullet_velocity" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="fire_rate" dataDxfId="9"/>
+    <tableColumn id="41" xr3:uid="{D6CEC36C-985A-453A-AC8C-074C80CDE463}" name="muzzle_loudness" dataDxfId="0"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="price" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="damage_torso_a" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="damage_torso_b" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="damage_torso_c" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="damage_torso_d" dataDxfId="4"/>
+    <tableColumn id="43" xr3:uid="{D5021237-E759-4A3A-B219-A4E638DB2DAD}" name="damage_arm_d" dataDxfId="3"/>
+    <tableColumn id="45" xr3:uid="{55603E35-2152-4FD3-9598-9256E449C5B0}" name="damage_leg_d" dataDxfId="2"/>
+    <tableColumn id="44" xr3:uid="{8CA87E20-CD33-48FB-A112-3BC0E2D56BD8}" name="damage_head_d" dataDxfId="1"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="damage_25"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="damage_75"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="damage_150"/>
@@ -999,7 +1040,9 @@
     <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="penetration"/>
     <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="calibers_row"/>
     <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="source_file"/>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="balance_score"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="balance_score">
+      <calculatedColumnFormula>C3*Model!$B$24+D3*Model!$B$25+E3*Model!$B$26+F3*Model!$B$27+G3*Model!$B$28+H3*Model!$B$29+I3*Model!$B$30+J3*Model!$B$31+K3*Model!$B$32+L3*Model!$B$33</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="damage_score"/>
     <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="velocity_drop_score"/>
     <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="suppression_score"/>
@@ -1205,13 +1248,13 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="L2" dT="2026-07-16T07:32:03.79" personId="{44D167D2-DCE2-4AD6-AB96-B8D142E6A4E1}" id="{A569BF01-BDF5-810D-9627-257FA0348527}">
+  <threadedComment ref="M2" dT="2026-07-16T07:32:03.79" personId="{44D167D2-DCE2-4AD6-AB96-B8D142E6A4E1}" id="{A569BF01-BDF5-810D-9627-257FA0348527}">
     <text>Direct values from calibers.csv. Edit these cells on this sheet to tune the ammo model.</text>
   </threadedComment>
-  <threadedComment ref="S2" dT="2026-07-16T07:33:16.03" personId="{44D167D2-DCE2-4AD6-AB96-B8D142E6A4E1}" id="{C50C973F-DB39-4CEA-6514-B39D616BCE25}">
+  <threadedComment ref="T2" dT="2026-07-16T07:33:16.03" personId="{44D167D2-DCE2-4AD6-AB96-B8D142E6A4E1}" id="{C50C973F-DB39-4CEA-6514-B39D616BCE25}">
     <text>Damage formula: MAX(MIN(a × distance + b, c) × d, 0). Distances and weights are on the Model sheet.</text>
   </threadedComment>
-  <threadedComment ref="AI2" dT="2026-07-16T07:33:16.03" personId="{44D167D2-DCE2-4AD6-AB96-B8D142E6A4E1}" id="{534C6D01-DEB9-6875-6EC6-551F5A30F31B}">
+  <threadedComment ref="AJ2" dT="2026-07-16T07:33:16.03" personId="{44D167D2-DCE2-4AD6-AB96-B8D142E6A4E1}" id="{534C6D01-DEB9-6875-6EC6-551F5A30F31B}">
     <text>Linearly interpolates effective velocity between pen_low/pen_high and clamps to those endpoints.</text>
   </threadedComment>
 </ThreadedComments>
@@ -1227,21 +1270,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AQ12"/>
+  <dimension ref="A1:AR12"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.125" customWidth="1"/>
     <col min="2" max="2" width="22.75" customWidth="1"/>
     <col min="3" max="8" width="5.625" customWidth="1"/>
     <col min="9" max="9" width="8" customWidth="1"/>
-    <col min="10" max="28" width="5.625" customWidth="1"/>
-    <col min="29" max="29" width="27.125" customWidth="1"/>
-    <col min="30" max="36" width="5.625" customWidth="1"/>
-    <col min="37" max="37" width="9.625" customWidth="1"/>
-    <col min="38" max="43" width="5.625" customWidth="1"/>
+    <col min="10" max="29" width="5.625" customWidth="1"/>
+    <col min="30" max="30" width="27.125" customWidth="1"/>
+    <col min="31" max="37" width="5.625" customWidth="1"/>
+    <col min="38" max="38" width="9.625" customWidth="1"/>
+    <col min="39" max="44" width="5.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="24" customHeight="1">
+    <row r="1" spans="1:44" ht="24" customHeight="1">
       <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
@@ -1255,52 +1298,53 @@
       <c r="I1" s="47"/>
       <c r="J1" s="47"/>
       <c r="K1" s="47"/>
-      <c r="L1" s="48" t="s">
+      <c r="L1" s="47"/>
+      <c r="M1" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="48"/>
       <c r="N1" s="48"/>
       <c r="O1" s="48"/>
-      <c r="P1" s="44"/>
+      <c r="P1" s="48"/>
       <c r="Q1" s="44"/>
       <c r="R1" s="44"/>
-      <c r="S1" s="49" t="s">
+      <c r="S1" s="44"/>
+      <c r="T1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="T1" s="49"/>
       <c r="U1" s="49"/>
       <c r="V1" s="49"/>
       <c r="W1" s="49"/>
       <c r="X1" s="49"/>
       <c r="Y1" s="49"/>
       <c r="Z1" s="49"/>
-      <c r="AA1" s="48" t="s">
+      <c r="AA1" s="49"/>
+      <c r="AB1" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="AB1" s="48"/>
       <c r="AC1" s="48"/>
       <c r="AD1" s="48"/>
       <c r="AE1" s="48"/>
       <c r="AF1" s="48"/>
       <c r="AG1" s="48"/>
-      <c r="AH1" s="50" t="s">
+      <c r="AH1" s="48"/>
+      <c r="AI1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="AI1" s="50"/>
-      <c r="AJ1" s="45" t="s">
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="AK1" s="45"/>
-      <c r="AL1" s="46" t="s">
+      <c r="AL1" s="45"/>
+      <c r="AM1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AM1" s="46"/>
       <c r="AN1" s="46"/>
       <c r="AO1" s="46"/>
       <c r="AP1" s="46"/>
       <c r="AQ1" s="46"/>
-    </row>
-    <row r="2" spans="1:43" ht="45.95" customHeight="1">
+      <c r="AR1" s="46"/>
+    </row>
+    <row r="2" spans="1:44" ht="45.95" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1332,106 +1376,109 @@
         <v>16</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AC2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AF2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AG2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AH2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AI2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AJ2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AK2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AL2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AM2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AN2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AN2" s="1" t="s">
+      <c r="AO2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AO2" s="1" t="s">
+      <c r="AP2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AP2" s="1" t="s">
+      <c r="AQ2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="AR2" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:43">
+    <row r="3" spans="1:44">
       <c r="A3" s="2" t="s">
         <v>47</v>
       </c>
@@ -1458,124 +1505,125 @@
         <v>0</v>
       </c>
       <c r="J3" s="7"/>
-      <c r="K3" s="41">
+      <c r="K3" s="7"/>
+      <c r="L3" s="41">
         <v>0</v>
       </c>
-      <c r="L3" s="3">
+      <c r="M3" s="3">
         <v>-2.5999999999999999E-2</v>
-      </c>
-      <c r="M3" s="3">
-        <v>56</v>
       </c>
       <c r="N3" s="3">
         <v>56</v>
       </c>
       <c r="O3" s="3">
+        <v>56</v>
+      </c>
+      <c r="P3" s="3">
         <v>1</v>
       </c>
-      <c r="P3" s="3">
+      <c r="Q3" s="3">
         <v>0.3</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="R3" s="3">
         <v>0.5</v>
       </c>
-      <c r="R3" s="3">
+      <c r="S3" s="3">
         <v>2.5</v>
       </c>
-      <c r="S3" s="13">
-        <f>MAX(MIN($L3*Model!$A$13+$M3,$N3)*$O3,0)</f>
+      <c r="T3" s="13">
+        <f>MAX(MIN($M3*Model!$A$13+$N3,$O3)*$P3,0)</f>
         <v>55.35</v>
       </c>
-      <c r="T3" s="13">
-        <f>MAX(MIN($L3*Model!$A$14+$M3,$N3)*$O3,0)</f>
+      <c r="U3" s="13">
+        <f>MAX(MIN($M3*Model!$A$14+$N3,$O3)*$P3,0)</f>
         <v>54.05</v>
       </c>
-      <c r="U3" s="13">
-        <f>MAX(MIN($L3*Model!$A$15+$M3,$N3)*$O3,0)</f>
+      <c r="V3" s="13">
+        <f>MAX(MIN($M3*Model!$A$15+$N3,$O3)*$P3,0)</f>
         <v>52.1</v>
       </c>
-      <c r="V3" s="13">
-        <f>MAX(MIN($L3*Model!$A$16+$M3,$N3)*$O3,0)</f>
+      <c r="W3" s="13">
+        <f>MAX(MIN($M3*Model!$A$16+$N3,$O3)*$P3,0)</f>
         <v>49.5</v>
       </c>
-      <c r="W3" s="13">
-        <f>MAX(MIN($L3*Model!$A$17+$M3,$N3)*$O3,0)</f>
+      <c r="X3" s="13">
+        <f>MAX(MIN($M3*Model!$A$17+$N3,$O3)*$P3,0)</f>
         <v>46.25</v>
       </c>
-      <c r="X3" s="13">
-        <f>MAX(MIN($L3*Model!$A$18+$M3,$N3)*$O3,0)</f>
+      <c r="Y3" s="13">
+        <f>MAX(MIN($M3*Model!$A$18+$N3,$O3)*$P3,0)</f>
         <v>45.6</v>
       </c>
-      <c r="Y3" s="13">
-        <f>MAX(MIN($L3*Model!$A$19+$M3,$N3)*$O3,0)</f>
+      <c r="Z3" s="13">
+        <f>MAX(MIN($M3*Model!$A$19+$N3,$O3)*$P3,0)</f>
         <v>43</v>
       </c>
-      <c r="Z3" s="13">
-        <f>S3*Model!$B$13+T3*Model!$B$14+U3*Model!$B$15+V3*Model!$B$16+W3*Model!$B$17+X3*Model!$B$18+Y3*Model!$B$19</f>
+      <c r="AA3" s="13">
+        <f>T3*Model!$B$13+U3*Model!$B$14+V3*Model!$B$15+W3*Model!$B$16+X3*Model!$B$17+Y3*Model!$B$18+Z3*Model!$B$19</f>
         <v>51.45</v>
       </c>
-      <c r="AA3" s="11">
+      <c r="AB3" s="11">
         <v>0.5</v>
       </c>
-      <c r="AB3" s="11">
+      <c r="AC3" s="11">
         <v>0.75</v>
       </c>
-      <c r="AC3" s="3" t="str">
+      <c r="AD3" s="3" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",AmmoChangeSheet[[#This Row],[pen_low]],";",AmmoChangeSheet[[#This Row],[pen_high]],";",AmmoChangeSheet[[#This Row],[pen_velocity_low]],";",AmmoChangeSheet[[#This Row],[pen_velocity_high]],")")</f>
         <v>stat(bullet_velocity;0.25;0.75;1500;3000)</v>
       </c>
-      <c r="AD3" s="11">
+      <c r="AE3" s="11">
         <v>0.25</v>
       </c>
-      <c r="AE3" s="11">
+      <c r="AF3" s="11">
         <v>0.75</v>
       </c>
-      <c r="AF3" s="15">
+      <c r="AG3" s="15">
         <v>1500</v>
       </c>
-      <c r="AG3" s="15">
+      <c r="AH3" s="15">
         <v>3000</v>
       </c>
-      <c r="AH3" s="16">
+      <c r="AI3" s="16">
         <f>Model!$B$4+IF(I3="",0,I3)</f>
         <v>2343</v>
       </c>
-      <c r="AI3" s="13">
-        <f t="shared" ref="AI3:AI12" si="0">MAX(AD3,MIN(AE3,AD3+(AH3-AF3)*(AE3-AD3)/(AG3-AF3)))</f>
+      <c r="AJ3" s="13">
+        <f t="shared" ref="AJ3:AJ12" si="0">MAX(AE3,MIN(AF3,AE3+(AI3-AG3)*(AF3-AE3)/(AH3-AG3)))</f>
         <v>0.53100000000000003</v>
       </c>
-      <c r="AJ3" s="19">
+      <c r="AK3" s="19">
         <v>19</v>
       </c>
-      <c r="AK3" s="4" t="s">
+      <c r="AL3" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AL3" s="21">
-        <f>C3*Model!$B$24+D3*Model!$B$25+E3*Model!$B$26+F3*Model!$B$27+G3*Model!$B$28+H3*Model!$B$29+I3*Model!$B$30+J3*Model!$B$31+K3*Model!$B$32</f>
+      <c r="AM3" s="21">
+        <f>C3*Model!$B$24+D3*Model!$B$25+E3*Model!$B$26+F3*Model!$B$27+G3*Model!$B$28+H3*Model!$B$29+I3*Model!$B$30+J3*Model!$B$31+K3*Model!$B$32+L3*Model!$B$33</f>
         <v>0</v>
       </c>
-      <c r="AM3" s="21">
-        <f>(Z3-Model!$B$5)*Model!$B$35</f>
+      <c r="AN3" s="21">
+        <f>(AA3-Model!$B$5)*Model!$B$36</f>
         <v>2.1750000000000043</v>
       </c>
-      <c r="AN3" s="21">
-        <f>(Model!$B$6-AA3)*Model!$B$36</f>
+      <c r="AO3" s="21">
+        <f>(Model!$B$6-AB3)*Model!$B$37</f>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="AO3" s="21">
-        <f>(AB3-Model!$B$7)*Model!$B$37</f>
+      <c r="AP3" s="21">
+        <f>(AC3-Model!$B$7)*Model!$B$38</f>
         <v>-0.29999999999999993</v>
       </c>
-      <c r="AP3" s="21">
-        <f>(AI3-Model!$B$8)*Model!$B$38</f>
+      <c r="AQ3" s="21">
+        <f>(AJ3-Model!$B$8)*Model!$B$39</f>
         <v>-1.8759999999999999</v>
       </c>
-      <c r="AQ3" s="21">
-        <f t="shared" ref="AQ3:AQ12" si="1">SUM(AL3:AP3)</f>
+      <c r="AR3" s="21">
+        <f t="shared" ref="AR3:AR12" si="1">SUM(AM3:AQ3)</f>
         <v>-0.30099999999999572</v>
       </c>
     </row>
-    <row r="4" spans="1:43">
+    <row r="4" spans="1:44">
       <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
@@ -1602,124 +1650,125 @@
         <v>25</v>
       </c>
       <c r="J4" s="7"/>
-      <c r="K4" s="41">
+      <c r="K4" s="7"/>
+      <c r="L4" s="41">
         <v>500</v>
       </c>
-      <c r="L4" s="3">
+      <c r="M4" s="3">
         <v>-2.8000000000000001E-2</v>
-      </c>
-      <c r="M4" s="3">
-        <v>55</v>
       </c>
       <c r="N4" s="3">
         <v>55</v>
       </c>
       <c r="O4" s="3">
+        <v>55</v>
+      </c>
+      <c r="P4" s="3">
         <v>1</v>
       </c>
-      <c r="P4" s="3">
+      <c r="Q4" s="3">
         <v>0.3</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="R4" s="3">
         <v>0.5</v>
       </c>
-      <c r="R4" s="3">
+      <c r="S4" s="3">
         <v>2.5</v>
       </c>
-      <c r="S4" s="13">
-        <f>MAX(MIN($L4*Model!$A$13+$M4,$N4)*$O4,0)</f>
+      <c r="T4" s="13">
+        <f>MAX(MIN($M4*Model!$A$13+$N4,$O4)*$P4,0)</f>
         <v>54.3</v>
       </c>
-      <c r="T4" s="13">
-        <f>MAX(MIN($L4*Model!$A$14+$M4,$N4)*$O4,0)</f>
+      <c r="U4" s="13">
+        <f>MAX(MIN($M4*Model!$A$14+$N4,$O4)*$P4,0)</f>
         <v>52.9</v>
       </c>
-      <c r="U4" s="13">
-        <f>MAX(MIN($L4*Model!$A$15+$M4,$N4)*$O4,0)</f>
+      <c r="V4" s="13">
+        <f>MAX(MIN($M4*Model!$A$15+$N4,$O4)*$P4,0)</f>
         <v>50.8</v>
       </c>
-      <c r="V4" s="13">
-        <f>MAX(MIN($L4*Model!$A$16+$M4,$N4)*$O4,0)</f>
+      <c r="W4" s="13">
+        <f>MAX(MIN($M4*Model!$A$16+$N4,$O4)*$P4,0)</f>
         <v>48</v>
       </c>
-      <c r="W4" s="13">
-        <f>MAX(MIN($L4*Model!$A$17+$M4,$N4)*$O4,0)</f>
+      <c r="X4" s="13">
+        <f>MAX(MIN($M4*Model!$A$17+$N4,$O4)*$P4,0)</f>
         <v>44.5</v>
       </c>
-      <c r="X4" s="13">
-        <f>MAX(MIN($L4*Model!$A$18+$M4,$N4)*$O4,0)</f>
+      <c r="Y4" s="13">
+        <f>MAX(MIN($M4*Model!$A$18+$N4,$O4)*$P4,0)</f>
         <v>43.8</v>
       </c>
-      <c r="Y4" s="13">
-        <f>MAX(MIN($L4*Model!$A$19+$M4,$N4)*$O4,0)</f>
+      <c r="Z4" s="13">
+        <f>MAX(MIN($M4*Model!$A$19+$N4,$O4)*$P4,0)</f>
         <v>41</v>
       </c>
-      <c r="Z4" s="13">
-        <f>S4*Model!$B$13+T4*Model!$B$14+U4*Model!$B$15+V4*Model!$B$16+W4*Model!$B$17+X4*Model!$B$18+Y4*Model!$B$19</f>
+      <c r="AA4" s="13">
+        <f>T4*Model!$B$13+U4*Model!$B$14+V4*Model!$B$15+W4*Model!$B$16+X4*Model!$B$17+Y4*Model!$B$18+Z4*Model!$B$19</f>
         <v>50.1</v>
       </c>
-      <c r="AA4" s="11">
+      <c r="AB4" s="11">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AB4" s="11">
+      <c r="AC4" s="11">
         <v>1.05</v>
       </c>
-      <c r="AC4" s="3" t="str">
+      <c r="AD4" s="3" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",AmmoChangeSheet[[#This Row],[pen_low]],";",AmmoChangeSheet[[#This Row],[pen_high]],";",AmmoChangeSheet[[#This Row],[pen_velocity_low]],";",AmmoChangeSheet[[#This Row],[pen_velocity_high]],")")</f>
         <v>stat(bullet_velocity;0.2;0.7;1500;3000)</v>
       </c>
-      <c r="AD4" s="11">
+      <c r="AE4" s="11">
         <v>0.2</v>
       </c>
-      <c r="AE4" s="11">
+      <c r="AF4" s="11">
         <v>0.7</v>
       </c>
-      <c r="AF4" s="15">
+      <c r="AG4" s="15">
         <v>1500</v>
       </c>
-      <c r="AG4" s="15">
+      <c r="AH4" s="15">
         <v>3000</v>
       </c>
-      <c r="AH4" s="16">
+      <c r="AI4" s="16">
         <f>Model!$B$4+IF(I4="",0,I4)</f>
         <v>2368</v>
       </c>
-      <c r="AI4" s="13">
+      <c r="AJ4" s="13">
         <f t="shared" si="0"/>
         <v>0.48933333333333329</v>
       </c>
-      <c r="AJ4" s="19">
+      <c r="AK4" s="19">
         <v>22</v>
       </c>
-      <c r="AK4" s="4" t="s">
+      <c r="AL4" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AL4" s="21">
-        <f>C4*Model!$B$24+D4*Model!$B$25+E4*Model!$B$26+F4*Model!$B$27+G4*Model!$B$28+H4*Model!$B$29+I4*Model!$B$30+J4*Model!$B$31+K4*Model!$B$32</f>
+      <c r="AM4" s="21">
+        <f>C4*Model!$B$24+D4*Model!$B$25+E4*Model!$B$26+F4*Model!$B$27+G4*Model!$B$28+H4*Model!$B$29+I4*Model!$B$30+J4*Model!$B$31+K4*Model!$B$32+L4*Model!$B$33</f>
         <v>2.4250000000000003</v>
       </c>
-      <c r="AM4" s="21">
-        <f>(Z4-Model!$B$5)*Model!$B$35</f>
+      <c r="AN4" s="21">
+        <f>(AA4-Model!$B$5)*Model!$B$36</f>
         <v>0.15000000000000213</v>
       </c>
-      <c r="AN4" s="21">
-        <f>(Model!$B$6-AA4)*Model!$B$36</f>
+      <c r="AO4" s="21">
+        <f>(Model!$B$6-AB4)*Model!$B$37</f>
         <v>-0.40000000000000013</v>
       </c>
-      <c r="AO4" s="21">
-        <f>(AB4-Model!$B$7)*Model!$B$37</f>
+      <c r="AP4" s="21">
+        <f>(AC4-Model!$B$7)*Model!$B$38</f>
         <v>0.6000000000000002</v>
       </c>
-      <c r="AP4" s="21">
-        <f>(AI4-Model!$B$8)*Model!$B$38</f>
+      <c r="AQ4" s="21">
+        <f>(AJ4-Model!$B$8)*Model!$B$39</f>
         <v>-2.0426666666666669</v>
       </c>
-      <c r="AQ4" s="21">
+      <c r="AR4" s="21">
         <f t="shared" si="1"/>
         <v>0.73233333333333572</v>
       </c>
     </row>
-    <row r="5" spans="1:43">
+    <row r="5" spans="1:44">
       <c r="A5" s="2" t="s">
         <v>52</v>
       </c>
@@ -1746,124 +1795,125 @@
         <v>-25</v>
       </c>
       <c r="J5" s="7"/>
-      <c r="K5" s="41">
+      <c r="K5" s="7"/>
+      <c r="L5" s="41">
         <v>750</v>
       </c>
-      <c r="L5" s="3">
+      <c r="M5" s="3">
         <v>-2.4E-2</v>
-      </c>
-      <c r="M5" s="3">
-        <v>56.5</v>
       </c>
       <c r="N5" s="3">
         <v>56.5</v>
       </c>
       <c r="O5" s="3">
+        <v>56.5</v>
+      </c>
+      <c r="P5" s="3">
         <v>1</v>
       </c>
-      <c r="P5" s="3">
+      <c r="Q5" s="3">
         <v>0.3</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="R5" s="3">
         <v>0.5</v>
       </c>
-      <c r="R5" s="3">
+      <c r="S5" s="3">
         <v>2.5</v>
       </c>
-      <c r="S5" s="13">
-        <f>MAX(MIN($L5*Model!$A$13+$M5,$N5)*$O5,0)</f>
+      <c r="T5" s="13">
+        <f>MAX(MIN($M5*Model!$A$13+$N5,$O5)*$P5,0)</f>
         <v>55.9</v>
       </c>
-      <c r="T5" s="13">
-        <f>MAX(MIN($L5*Model!$A$14+$M5,$N5)*$O5,0)</f>
+      <c r="U5" s="13">
+        <f>MAX(MIN($M5*Model!$A$14+$N5,$O5)*$P5,0)</f>
         <v>54.7</v>
       </c>
-      <c r="U5" s="13">
-        <f>MAX(MIN($L5*Model!$A$15+$M5,$N5)*$O5,0)</f>
+      <c r="V5" s="13">
+        <f>MAX(MIN($M5*Model!$A$15+$N5,$O5)*$P5,0)</f>
         <v>52.9</v>
       </c>
-      <c r="V5" s="13">
-        <f>MAX(MIN($L5*Model!$A$16+$M5,$N5)*$O5,0)</f>
+      <c r="W5" s="13">
+        <f>MAX(MIN($M5*Model!$A$16+$N5,$O5)*$P5,0)</f>
         <v>50.5</v>
       </c>
-      <c r="W5" s="13">
-        <f>MAX(MIN($L5*Model!$A$17+$M5,$N5)*$O5,0)</f>
+      <c r="X5" s="13">
+        <f>MAX(MIN($M5*Model!$A$17+$N5,$O5)*$P5,0)</f>
         <v>47.5</v>
       </c>
-      <c r="X5" s="13">
-        <f>MAX(MIN($L5*Model!$A$18+$M5,$N5)*$O5,0)</f>
+      <c r="Y5" s="13">
+        <f>MAX(MIN($M5*Model!$A$18+$N5,$O5)*$P5,0)</f>
         <v>46.9</v>
       </c>
-      <c r="Y5" s="13">
-        <f>MAX(MIN($L5*Model!$A$19+$M5,$N5)*$O5,0)</f>
+      <c r="Z5" s="13">
+        <f>MAX(MIN($M5*Model!$A$19+$N5,$O5)*$P5,0)</f>
         <v>44.5</v>
       </c>
-      <c r="Z5" s="13">
-        <f>S5*Model!$B$13+T5*Model!$B$14+U5*Model!$B$15+V5*Model!$B$16+W5*Model!$B$17+X5*Model!$B$18+Y5*Model!$B$19</f>
+      <c r="AA5" s="13">
+        <f>T5*Model!$B$13+U5*Model!$B$14+V5*Model!$B$15+W5*Model!$B$16+X5*Model!$B$17+Y5*Model!$B$18+Z5*Model!$B$19</f>
         <v>52.300000000000004</v>
       </c>
-      <c r="AA5" s="11">
+      <c r="AB5" s="11">
         <v>0.45</v>
       </c>
-      <c r="AB5" s="11">
+      <c r="AC5" s="11">
         <v>0.75</v>
       </c>
-      <c r="AC5" s="3" t="str">
+      <c r="AD5" s="3" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",AmmoChangeSheet[[#This Row],[pen_low]],";",AmmoChangeSheet[[#This Row],[pen_high]],";",AmmoChangeSheet[[#This Row],[pen_velocity_low]],";",AmmoChangeSheet[[#This Row],[pen_velocity_high]],")")</f>
         <v>stat(bullet_velocity;0.35;0.85;1500;3000)</v>
       </c>
-      <c r="AD5" s="11">
+      <c r="AE5" s="11">
         <v>0.35</v>
       </c>
-      <c r="AE5" s="11">
+      <c r="AF5" s="11">
         <v>0.85</v>
       </c>
-      <c r="AF5" s="15">
+      <c r="AG5" s="15">
         <v>1500</v>
       </c>
-      <c r="AG5" s="15">
+      <c r="AH5" s="15">
         <v>3000</v>
       </c>
-      <c r="AH5" s="16">
+      <c r="AI5" s="16">
         <f>Model!$B$4+IF(I5="",0,I5)</f>
         <v>2318</v>
       </c>
-      <c r="AI5" s="13">
+      <c r="AJ5" s="13">
         <f t="shared" si="0"/>
         <v>0.6226666666666667</v>
       </c>
-      <c r="AJ5" s="19">
+      <c r="AK5" s="19">
         <v>25</v>
       </c>
-      <c r="AK5" s="4" t="s">
+      <c r="AL5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AL5" s="21">
-        <f>C5*Model!$B$24+D5*Model!$B$25+E5*Model!$B$26+F5*Model!$B$27+G5*Model!$B$28+H5*Model!$B$29+I5*Model!$B$30+J5*Model!$B$31+K5*Model!$B$32</f>
+      <c r="AM5" s="21">
+        <f>C5*Model!$B$24+D5*Model!$B$25+E5*Model!$B$26+F5*Model!$B$27+G5*Model!$B$28+H5*Model!$B$29+I5*Model!$B$30+J5*Model!$B$31+K5*Model!$B$32+L5*Model!$B$33</f>
         <v>-1.625</v>
       </c>
-      <c r="AM5" s="21">
-        <f>(Z5-Model!$B$5)*Model!$B$35</f>
+      <c r="AN5" s="21">
+        <f>(AA5-Model!$B$5)*Model!$B$36</f>
         <v>3.4500000000000064</v>
       </c>
-      <c r="AN5" s="21">
-        <f>(Model!$B$6-AA5)*Model!$B$36</f>
+      <c r="AO5" s="21">
+        <f>(Model!$B$6-AB5)*Model!$B$37</f>
         <v>-0.20000000000000007</v>
       </c>
-      <c r="AO5" s="21">
-        <f>(AB5-Model!$B$7)*Model!$B$37</f>
+      <c r="AP5" s="21">
+        <f>(AC5-Model!$B$7)*Model!$B$38</f>
         <v>-0.29999999999999993</v>
       </c>
-      <c r="AP5" s="21">
-        <f>(AI5-Model!$B$8)*Model!$B$38</f>
+      <c r="AQ5" s="21">
+        <f>(AJ5-Model!$B$8)*Model!$B$39</f>
         <v>-1.5093333333333332</v>
       </c>
-      <c r="AQ5" s="21">
+      <c r="AR5" s="21">
         <f t="shared" si="1"/>
         <v>-0.1843333333333268</v>
       </c>
     </row>
-    <row r="6" spans="1:43">
+    <row r="6" spans="1:44">
       <c r="A6" s="2" t="s">
         <v>54</v>
       </c>
@@ -1890,124 +1940,125 @@
         <v>-25</v>
       </c>
       <c r="J6" s="7"/>
-      <c r="K6" s="41">
+      <c r="K6" s="7"/>
+      <c r="L6" s="41">
         <v>1250</v>
       </c>
-      <c r="L6" s="3">
+      <c r="M6" s="3">
         <v>-2.1999999999999999E-2</v>
       </c>
-      <c r="M6" s="3">
+      <c r="N6" s="3">
         <v>54.5</v>
       </c>
-      <c r="N6" s="3">
+      <c r="O6" s="3">
         <v>53</v>
       </c>
-      <c r="O6" s="3">
+      <c r="P6" s="3">
         <v>1</v>
       </c>
-      <c r="P6" s="3">
+      <c r="Q6" s="3">
         <v>0.25</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="R6" s="3">
         <v>0.45</v>
       </c>
-      <c r="R6" s="3">
+      <c r="S6" s="3">
         <v>2.5</v>
       </c>
-      <c r="S6" s="13">
-        <f>MAX(MIN($L6*Model!$A$13+$M6,$N6)*$O6,0)</f>
+      <c r="T6" s="13">
+        <f>MAX(MIN($M6*Model!$A$13+$N6,$O6)*$P6,0)</f>
         <v>53</v>
       </c>
-      <c r="T6" s="13">
-        <f>MAX(MIN($L6*Model!$A$14+$M6,$N6)*$O6,0)</f>
+      <c r="U6" s="13">
+        <f>MAX(MIN($M6*Model!$A$14+$N6,$O6)*$P6,0)</f>
         <v>52.85</v>
       </c>
-      <c r="U6" s="13">
-        <f>MAX(MIN($L6*Model!$A$15+$M6,$N6)*$O6,0)</f>
+      <c r="V6" s="13">
+        <f>MAX(MIN($M6*Model!$A$15+$N6,$O6)*$P6,0)</f>
         <v>51.2</v>
       </c>
-      <c r="V6" s="13">
-        <f>MAX(MIN($L6*Model!$A$16+$M6,$N6)*$O6,0)</f>
+      <c r="W6" s="13">
+        <f>MAX(MIN($M6*Model!$A$16+$N6,$O6)*$P6,0)</f>
         <v>49</v>
       </c>
-      <c r="W6" s="13">
-        <f>MAX(MIN($L6*Model!$A$17+$M6,$N6)*$O6,0)</f>
+      <c r="X6" s="13">
+        <f>MAX(MIN($M6*Model!$A$17+$N6,$O6)*$P6,0)</f>
         <v>46.25</v>
       </c>
-      <c r="X6" s="13">
-        <f>MAX(MIN($L6*Model!$A$18+$M6,$N6)*$O6,0)</f>
+      <c r="Y6" s="13">
+        <f>MAX(MIN($M6*Model!$A$18+$N6,$O6)*$P6,0)</f>
         <v>45.7</v>
       </c>
-      <c r="Y6" s="13">
-        <f>MAX(MIN($L6*Model!$A$19+$M6,$N6)*$O6,0)</f>
+      <c r="Z6" s="13">
+        <f>MAX(MIN($M6*Model!$A$19+$N6,$O6)*$P6,0)</f>
         <v>43.5</v>
       </c>
-      <c r="Z6" s="13">
-        <f>S6*Model!$B$13+T6*Model!$B$14+U6*Model!$B$15+V6*Model!$B$16+W6*Model!$B$17+X6*Model!$B$18+Y6*Model!$B$19</f>
+      <c r="AA6" s="13">
+        <f>T6*Model!$B$13+U6*Model!$B$14+V6*Model!$B$15+W6*Model!$B$16+X6*Model!$B$17+Y6*Model!$B$18+Z6*Model!$B$19</f>
         <v>50.460000000000008</v>
       </c>
-      <c r="AA6" s="11">
+      <c r="AB6" s="11">
         <v>0.45</v>
       </c>
-      <c r="AB6" s="11">
+      <c r="AC6" s="11">
         <v>0.8</v>
       </c>
-      <c r="AC6" s="3" t="str">
+      <c r="AD6" s="3" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",AmmoChangeSheet[[#This Row],[pen_low]],";",AmmoChangeSheet[[#This Row],[pen_high]],";",AmmoChangeSheet[[#This Row],[pen_velocity_low]],";",AmmoChangeSheet[[#This Row],[pen_velocity_high]],")")</f>
         <v>stat(bullet_velocity;0.8;1.3;1500;3000)</v>
       </c>
-      <c r="AD6" s="11">
+      <c r="AE6" s="11">
         <v>0.8</v>
       </c>
-      <c r="AE6" s="11">
+      <c r="AF6" s="11">
         <v>1.3</v>
       </c>
-      <c r="AF6" s="15">
+      <c r="AG6" s="15">
         <v>1500</v>
       </c>
-      <c r="AG6" s="15">
+      <c r="AH6" s="15">
         <v>3000</v>
       </c>
-      <c r="AH6" s="16">
+      <c r="AI6" s="16">
         <f>Model!$B$4+IF(I6="",0,I6)</f>
         <v>2318</v>
       </c>
-      <c r="AI6" s="13">
+      <c r="AJ6" s="13">
         <f t="shared" si="0"/>
         <v>1.0726666666666667</v>
       </c>
-      <c r="AJ6" s="19">
+      <c r="AK6" s="19">
         <v>21</v>
       </c>
-      <c r="AK6" s="4" t="s">
+      <c r="AL6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AL6" s="21">
-        <f>C6*Model!$B$24+D6*Model!$B$25+E6*Model!$B$26+F6*Model!$B$27+G6*Model!$B$28+H6*Model!$B$29+I6*Model!$B$30+J6*Model!$B$31+K6*Model!$B$32</f>
+      <c r="AM6" s="21">
+        <f>C6*Model!$B$24+D6*Model!$B$25+E6*Model!$B$26+F6*Model!$B$27+G6*Model!$B$28+H6*Model!$B$29+I6*Model!$B$30+J6*Model!$B$31+K6*Model!$B$32+L6*Model!$B$33</f>
         <v>-0.52500000000000002</v>
       </c>
-      <c r="AM6" s="21">
-        <f>(Z6-Model!$B$5)*Model!$B$35</f>
+      <c r="AN6" s="21">
+        <f>(AA6-Model!$B$5)*Model!$B$36</f>
         <v>0.69000000000001194</v>
       </c>
-      <c r="AN6" s="21">
-        <f>(Model!$B$6-AA6)*Model!$B$36</f>
+      <c r="AO6" s="21">
+        <f>(Model!$B$6-AB6)*Model!$B$37</f>
         <v>-0.20000000000000007</v>
       </c>
-      <c r="AO6" s="21">
-        <f>(AB6-Model!$B$7)*Model!$B$37</f>
+      <c r="AP6" s="21">
+        <f>(AC6-Model!$B$7)*Model!$B$38</f>
         <v>-0.1499999999999998</v>
       </c>
-      <c r="AP6" s="21">
-        <f>(AI6-Model!$B$8)*Model!$B$38</f>
+      <c r="AQ6" s="21">
+        <f>(AJ6-Model!$B$8)*Model!$B$39</f>
         <v>0.29066666666666663</v>
       </c>
-      <c r="AQ6" s="21">
+      <c r="AR6" s="21">
         <f t="shared" si="1"/>
         <v>0.10566666666667868</v>
       </c>
     </row>
-    <row r="7" spans="1:43">
+    <row r="7" spans="1:44">
       <c r="A7" s="2" t="s">
         <v>56</v>
       </c>
@@ -2034,124 +2085,125 @@
         <v>-75</v>
       </c>
       <c r="J7" s="7"/>
-      <c r="K7" s="41">
+      <c r="K7" s="7"/>
+      <c r="L7" s="41">
         <v>1000</v>
       </c>
-      <c r="L7" s="3">
+      <c r="M7" s="3">
         <v>-3.4000000000000002E-2</v>
       </c>
-      <c r="M7" s="3">
+      <c r="N7" s="3">
         <v>60</v>
       </c>
-      <c r="N7" s="3">
+      <c r="O7" s="3">
         <v>59</v>
       </c>
-      <c r="O7" s="3">
+      <c r="P7" s="3">
         <v>1</v>
       </c>
-      <c r="P7" s="3">
+      <c r="Q7" s="3">
         <v>0.3</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="R7" s="3">
         <v>0.5</v>
       </c>
-      <c r="R7" s="3">
+      <c r="S7" s="3">
         <v>2.5</v>
       </c>
-      <c r="S7" s="13">
-        <f>MAX(MIN($L7*Model!$A$13+$M7,$N7)*$O7,0)</f>
+      <c r="T7" s="13">
+        <f>MAX(MIN($M7*Model!$A$13+$N7,$O7)*$P7,0)</f>
         <v>59</v>
       </c>
-      <c r="T7" s="13">
-        <f>MAX(MIN($L7*Model!$A$14+$M7,$N7)*$O7,0)</f>
+      <c r="U7" s="13">
+        <f>MAX(MIN($M7*Model!$A$14+$N7,$O7)*$P7,0)</f>
         <v>57.45</v>
       </c>
-      <c r="U7" s="13">
-        <f>MAX(MIN($L7*Model!$A$15+$M7,$N7)*$O7,0)</f>
+      <c r="V7" s="13">
+        <f>MAX(MIN($M7*Model!$A$15+$N7,$O7)*$P7,0)</f>
         <v>54.9</v>
       </c>
-      <c r="V7" s="13">
-        <f>MAX(MIN($L7*Model!$A$16+$M7,$N7)*$O7,0)</f>
+      <c r="W7" s="13">
+        <f>MAX(MIN($M7*Model!$A$16+$N7,$O7)*$P7,0)</f>
         <v>51.5</v>
       </c>
-      <c r="W7" s="13">
-        <f>MAX(MIN($L7*Model!$A$17+$M7,$N7)*$O7,0)</f>
+      <c r="X7" s="13">
+        <f>MAX(MIN($M7*Model!$A$17+$N7,$O7)*$P7,0)</f>
         <v>47.25</v>
       </c>
-      <c r="X7" s="13">
-        <f>MAX(MIN($L7*Model!$A$18+$M7,$N7)*$O7,0)</f>
+      <c r="Y7" s="13">
+        <f>MAX(MIN($M7*Model!$A$18+$N7,$O7)*$P7,0)</f>
         <v>46.4</v>
       </c>
-      <c r="Y7" s="13">
-        <f>MAX(MIN($L7*Model!$A$19+$M7,$N7)*$O7,0)</f>
+      <c r="Z7" s="13">
+        <f>MAX(MIN($M7*Model!$A$19+$N7,$O7)*$P7,0)</f>
         <v>43</v>
       </c>
-      <c r="Z7" s="13">
-        <f>S7*Model!$B$13+T7*Model!$B$14+U7*Model!$B$15+V7*Model!$B$16+W7*Model!$B$17+X7*Model!$B$18+Y7*Model!$B$19</f>
+      <c r="AA7" s="13">
+        <f>T7*Model!$B$13+U7*Model!$B$14+V7*Model!$B$15+W7*Model!$B$16+X7*Model!$B$17+Y7*Model!$B$18+Z7*Model!$B$19</f>
         <v>54.02000000000001</v>
       </c>
-      <c r="AA7" s="11">
+      <c r="AB7" s="11">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AB7" s="11">
+      <c r="AC7" s="11">
         <v>0.8</v>
       </c>
-      <c r="AC7" s="3" t="str">
+      <c r="AD7" s="3" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",AmmoChangeSheet[[#This Row],[pen_low]],";",AmmoChangeSheet[[#This Row],[pen_high]],";",AmmoChangeSheet[[#This Row],[pen_velocity_low]],";",AmmoChangeSheet[[#This Row],[pen_velocity_high]],")")</f>
         <v>stat(bullet_velocity;0.35;0.85;1500;3000)</v>
       </c>
-      <c r="AD7" s="11">
+      <c r="AE7" s="11">
         <v>0.35</v>
       </c>
-      <c r="AE7" s="11">
+      <c r="AF7" s="11">
         <v>0.85</v>
       </c>
-      <c r="AF7" s="15">
+      <c r="AG7" s="15">
         <v>1500</v>
       </c>
-      <c r="AG7" s="15">
+      <c r="AH7" s="15">
         <v>3000</v>
       </c>
-      <c r="AH7" s="16">
+      <c r="AI7" s="16">
         <f>Model!$B$4+IF(I7="",0,I7)</f>
         <v>2268</v>
       </c>
-      <c r="AI7" s="13">
+      <c r="AJ7" s="13">
         <f t="shared" si="0"/>
         <v>0.60599999999999998</v>
       </c>
-      <c r="AJ7" s="19">
+      <c r="AK7" s="19">
         <v>20</v>
       </c>
-      <c r="AK7" s="4" t="s">
+      <c r="AL7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AL7" s="21">
-        <f>C7*Model!$B$24+D7*Model!$B$25+E7*Model!$B$26+F7*Model!$B$27+G7*Model!$B$28+H7*Model!$B$29+I7*Model!$B$30+J7*Model!$B$31+K7*Model!$B$32</f>
+      <c r="AM7" s="21">
+        <f>C7*Model!$B$24+D7*Model!$B$25+E7*Model!$B$26+F7*Model!$B$27+G7*Model!$B$28+H7*Model!$B$29+I7*Model!$B$30+J7*Model!$B$31+K7*Model!$B$32+L7*Model!$B$33</f>
         <v>-2.875</v>
       </c>
-      <c r="AM7" s="21">
-        <f>(Z7-Model!$B$5)*Model!$B$35</f>
+      <c r="AN7" s="21">
+        <f>(AA7-Model!$B$5)*Model!$B$36</f>
         <v>6.0300000000000153</v>
       </c>
-      <c r="AN7" s="21">
-        <f>(Model!$B$6-AA7)*Model!$B$36</f>
+      <c r="AO7" s="21">
+        <f>(Model!$B$6-AB7)*Model!$B$37</f>
         <v>-0.40000000000000013</v>
       </c>
-      <c r="AO7" s="21">
-        <f>(AB7-Model!$B$7)*Model!$B$37</f>
+      <c r="AP7" s="21">
+        <f>(AC7-Model!$B$7)*Model!$B$38</f>
         <v>-0.1499999999999998</v>
       </c>
-      <c r="AP7" s="21">
-        <f>(AI7-Model!$B$8)*Model!$B$38</f>
+      <c r="AQ7" s="21">
+        <f>(AJ7-Model!$B$8)*Model!$B$39</f>
         <v>-1.5760000000000001</v>
       </c>
-      <c r="AQ7" s="21">
+      <c r="AR7" s="21">
         <f t="shared" si="1"/>
         <v>1.029000000000015</v>
       </c>
     </row>
-    <row r="8" spans="1:43">
+    <row r="8" spans="1:44">
       <c r="A8" s="2" t="s">
         <v>58</v>
       </c>
@@ -2178,124 +2230,125 @@
         <v>-25</v>
       </c>
       <c r="J8" s="7"/>
-      <c r="K8" s="41">
+      <c r="K8" s="7"/>
+      <c r="L8" s="41">
         <v>2000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>-1.6E-2</v>
-      </c>
-      <c r="M8" s="3">
-        <v>56</v>
       </c>
       <c r="N8" s="3">
         <v>56</v>
       </c>
       <c r="O8" s="3">
+        <v>56</v>
+      </c>
+      <c r="P8" s="3">
         <v>1</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>0.3</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>0.5</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2.5</v>
       </c>
-      <c r="S8" s="13">
-        <f>MAX(MIN($L8*Model!$A$13+$M8,$N8)*$O8,0)</f>
+      <c r="T8" s="13">
+        <f>MAX(MIN($M8*Model!$A$13+$N8,$O8)*$P8,0)</f>
         <v>55.6</v>
       </c>
-      <c r="T8" s="13">
-        <f>MAX(MIN($L8*Model!$A$14+$M8,$N8)*$O8,0)</f>
+      <c r="U8" s="13">
+        <f>MAX(MIN($M8*Model!$A$14+$N8,$O8)*$P8,0)</f>
         <v>54.8</v>
       </c>
-      <c r="U8" s="13">
-        <f>MAX(MIN($L8*Model!$A$15+$M8,$N8)*$O8,0)</f>
+      <c r="V8" s="13">
+        <f>MAX(MIN($M8*Model!$A$15+$N8,$O8)*$P8,0)</f>
         <v>53.6</v>
       </c>
-      <c r="V8" s="13">
-        <f>MAX(MIN($L8*Model!$A$16+$M8,$N8)*$O8,0)</f>
+      <c r="W8" s="13">
+        <f>MAX(MIN($M8*Model!$A$16+$N8,$O8)*$P8,0)</f>
         <v>52</v>
       </c>
-      <c r="W8" s="13">
-        <f>MAX(MIN($L8*Model!$A$17+$M8,$N8)*$O8,0)</f>
+      <c r="X8" s="13">
+        <f>MAX(MIN($M8*Model!$A$17+$N8,$O8)*$P8,0)</f>
         <v>50</v>
       </c>
-      <c r="X8" s="13">
-        <f>MAX(MIN($L8*Model!$A$18+$M8,$N8)*$O8,0)</f>
+      <c r="Y8" s="13">
+        <f>MAX(MIN($M8*Model!$A$18+$N8,$O8)*$P8,0)</f>
         <v>49.6</v>
       </c>
-      <c r="Y8" s="13">
-        <f>MAX(MIN($L8*Model!$A$19+$M8,$N8)*$O8,0)</f>
+      <c r="Z8" s="13">
+        <f>MAX(MIN($M8*Model!$A$19+$N8,$O8)*$P8,0)</f>
         <v>48</v>
       </c>
-      <c r="Z8" s="13">
-        <f>S8*Model!$B$13+T8*Model!$B$14+U8*Model!$B$15+V8*Model!$B$16+W8*Model!$B$17+X8*Model!$B$18+Y8*Model!$B$19</f>
+      <c r="AA8" s="13">
+        <f>T8*Model!$B$13+U8*Model!$B$14+V8*Model!$B$15+W8*Model!$B$16+X8*Model!$B$17+Y8*Model!$B$18+Z8*Model!$B$19</f>
         <v>53.2</v>
       </c>
-      <c r="AA8" s="11">
+      <c r="AB8" s="11">
         <v>0.4</v>
       </c>
-      <c r="AB8" s="11">
+      <c r="AC8" s="11">
         <v>0.7</v>
       </c>
-      <c r="AC8" s="3" t="str">
+      <c r="AD8" s="3" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",AmmoChangeSheet[[#This Row],[pen_low]],";",AmmoChangeSheet[[#This Row],[pen_high]],";",AmmoChangeSheet[[#This Row],[pen_velocity_low]],";",AmmoChangeSheet[[#This Row],[pen_velocity_high]],")")</f>
         <v>stat(bullet_velocity;0.2;0.7;1500;3000)</v>
       </c>
-      <c r="AD8" s="11">
+      <c r="AE8" s="11">
         <v>0.2</v>
       </c>
-      <c r="AE8" s="11">
+      <c r="AF8" s="11">
         <v>0.7</v>
       </c>
-      <c r="AF8" s="15">
+      <c r="AG8" s="15">
         <v>1500</v>
       </c>
-      <c r="AG8" s="15">
+      <c r="AH8" s="15">
         <v>3000</v>
       </c>
-      <c r="AH8" s="16">
+      <c r="AI8" s="16">
         <f>Model!$B$4+IF(I8="",0,I8)</f>
         <v>2318</v>
       </c>
-      <c r="AI8" s="13">
+      <c r="AJ8" s="13">
         <f t="shared" si="0"/>
         <v>0.47266666666666662</v>
       </c>
-      <c r="AJ8" s="19">
+      <c r="AK8" s="19">
         <v>17</v>
       </c>
-      <c r="AK8" s="4" t="s">
+      <c r="AL8" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AL8" s="21">
-        <f>C8*Model!$B$24+D8*Model!$B$25+E8*Model!$B$26+F8*Model!$B$27+G8*Model!$B$28+H8*Model!$B$29+I8*Model!$B$30+J8*Model!$B$31+K8*Model!$B$32</f>
+      <c r="AM8" s="21">
+        <f>C8*Model!$B$24+D8*Model!$B$25+E8*Model!$B$26+F8*Model!$B$27+G8*Model!$B$28+H8*Model!$B$29+I8*Model!$B$30+J8*Model!$B$31+K8*Model!$B$32+L8*Model!$B$33</f>
         <v>-1.125</v>
       </c>
-      <c r="AM8" s="21">
-        <f>(Z8-Model!$B$5)*Model!$B$35</f>
+      <c r="AN8" s="21">
+        <f>(AA8-Model!$B$5)*Model!$B$36</f>
         <v>4.8000000000000043</v>
       </c>
-      <c r="AN8" s="21">
-        <f>(Model!$B$6-AA8)*Model!$B$36</f>
+      <c r="AO8" s="21">
+        <f>(Model!$B$6-AB8)*Model!$B$37</f>
         <v>-0.10000000000000009</v>
       </c>
-      <c r="AO8" s="21">
-        <f>(AB8-Model!$B$7)*Model!$B$37</f>
+      <c r="AP8" s="21">
+        <f>(AC8-Model!$B$7)*Model!$B$38</f>
         <v>-0.45000000000000007</v>
       </c>
-      <c r="AP8" s="21">
-        <f>(AI8-Model!$B$8)*Model!$B$38</f>
+      <c r="AQ8" s="21">
+        <f>(AJ8-Model!$B$8)*Model!$B$39</f>
         <v>-2.1093333333333337</v>
       </c>
-      <c r="AQ8" s="21">
+      <c r="AR8" s="21">
         <f t="shared" si="1"/>
         <v>1.0156666666666703</v>
       </c>
     </row>
-    <row r="9" spans="1:43">
+    <row r="9" spans="1:44">
       <c r="A9" s="2" t="s">
         <v>60</v>
       </c>
@@ -2322,124 +2375,125 @@
         <v>-100</v>
       </c>
       <c r="J9" s="7"/>
-      <c r="K9" s="41">
+      <c r="K9" s="7"/>
+      <c r="L9" s="41">
         <v>2500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>-0.02</v>
-      </c>
-      <c r="M9" s="3">
-        <v>58</v>
       </c>
       <c r="N9" s="3">
         <v>58</v>
       </c>
       <c r="O9" s="3">
+        <v>58</v>
+      </c>
+      <c r="P9" s="3">
         <v>1</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>0.3</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>0.5</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2.5</v>
       </c>
-      <c r="S9" s="13">
-        <f>MAX(MIN($L9*Model!$A$13+$M9,$N9)*$O9,0)</f>
+      <c r="T9" s="13">
+        <f>MAX(MIN($M9*Model!$A$13+$N9,$O9)*$P9,0)</f>
         <v>57.5</v>
       </c>
-      <c r="T9" s="13">
-        <f>MAX(MIN($L9*Model!$A$14+$M9,$N9)*$O9,0)</f>
+      <c r="U9" s="13">
+        <f>MAX(MIN($M9*Model!$A$14+$N9,$O9)*$P9,0)</f>
         <v>56.5</v>
       </c>
-      <c r="U9" s="13">
-        <f>MAX(MIN($L9*Model!$A$15+$M9,$N9)*$O9,0)</f>
+      <c r="V9" s="13">
+        <f>MAX(MIN($M9*Model!$A$15+$N9,$O9)*$P9,0)</f>
         <v>55</v>
       </c>
-      <c r="V9" s="13">
-        <f>MAX(MIN($L9*Model!$A$16+$M9,$N9)*$O9,0)</f>
+      <c r="W9" s="13">
+        <f>MAX(MIN($M9*Model!$A$16+$N9,$O9)*$P9,0)</f>
         <v>53</v>
       </c>
-      <c r="W9" s="13">
-        <f>MAX(MIN($L9*Model!$A$17+$M9,$N9)*$O9,0)</f>
+      <c r="X9" s="13">
+        <f>MAX(MIN($M9*Model!$A$17+$N9,$O9)*$P9,0)</f>
         <v>50.5</v>
       </c>
-      <c r="X9" s="13">
-        <f>MAX(MIN($L9*Model!$A$18+$M9,$N9)*$O9,0)</f>
+      <c r="Y9" s="13">
+        <f>MAX(MIN($M9*Model!$A$18+$N9,$O9)*$P9,0)</f>
         <v>50</v>
       </c>
-      <c r="Y9" s="13">
-        <f>MAX(MIN($L9*Model!$A$19+$M9,$N9)*$O9,0)</f>
+      <c r="Z9" s="13">
+        <f>MAX(MIN($M9*Model!$A$19+$N9,$O9)*$P9,0)</f>
         <v>48</v>
       </c>
-      <c r="Z9" s="13">
-        <f>S9*Model!$B$13+T9*Model!$B$14+U9*Model!$B$15+V9*Model!$B$16+W9*Model!$B$17+X9*Model!$B$18+Y9*Model!$B$19</f>
+      <c r="AA9" s="13">
+        <f>T9*Model!$B$13+U9*Model!$B$14+V9*Model!$B$15+W9*Model!$B$16+X9*Model!$B$17+Y9*Model!$B$18+Z9*Model!$B$19</f>
         <v>54.5</v>
       </c>
-      <c r="AA9" s="11">
+      <c r="AB9" s="11">
         <v>0.35</v>
       </c>
-      <c r="AB9" s="11">
+      <c r="AC9" s="11">
         <v>0.75</v>
       </c>
-      <c r="AC9" s="3" t="str">
+      <c r="AD9" s="3" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",AmmoChangeSheet[[#This Row],[pen_low]],";",AmmoChangeSheet[[#This Row],[pen_high]],";",AmmoChangeSheet[[#This Row],[pen_velocity_low]],";",AmmoChangeSheet[[#This Row],[pen_velocity_high]],")")</f>
         <v>stat(bullet_velocity;0.15;0.65;1500;3000)</v>
       </c>
-      <c r="AD9" s="11">
+      <c r="AE9" s="11">
         <v>0.15</v>
       </c>
-      <c r="AE9" s="11">
+      <c r="AF9" s="11">
         <v>0.65</v>
       </c>
-      <c r="AF9" s="15">
+      <c r="AG9" s="15">
         <v>1500</v>
       </c>
-      <c r="AG9" s="15">
+      <c r="AH9" s="15">
         <v>3000</v>
       </c>
-      <c r="AH9" s="16">
+      <c r="AI9" s="16">
         <f>Model!$B$4+IF(I9="",0,I9)</f>
         <v>2243</v>
       </c>
-      <c r="AI9" s="13">
+      <c r="AJ9" s="13">
         <f t="shared" si="0"/>
         <v>0.39766666666666667</v>
       </c>
-      <c r="AJ9" s="19">
+      <c r="AK9" s="19">
         <v>18</v>
       </c>
-      <c r="AK9" s="4" t="s">
+      <c r="AL9" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AL9" s="21">
-        <f>C9*Model!$B$24+D9*Model!$B$25+E9*Model!$B$26+F9*Model!$B$27+G9*Model!$B$28+H9*Model!$B$29+I9*Model!$B$30+J9*Model!$B$31+K9*Model!$B$32</f>
+      <c r="AM9" s="21">
+        <f>C9*Model!$B$24+D9*Model!$B$25+E9*Model!$B$26+F9*Model!$B$27+G9*Model!$B$28+H9*Model!$B$29+I9*Model!$B$30+J9*Model!$B$31+K9*Model!$B$32+L9*Model!$B$33</f>
         <v>-2.3000000000000003</v>
       </c>
-      <c r="AM9" s="21">
-        <f>(Z9-Model!$B$5)*Model!$B$35</f>
+      <c r="AN9" s="21">
+        <f>(AA9-Model!$B$5)*Model!$B$36</f>
         <v>6.75</v>
       </c>
-      <c r="AN9" s="21">
-        <f>(Model!$B$6-AA9)*Model!$B$36</f>
+      <c r="AO9" s="21">
+        <f>(Model!$B$6-AB9)*Model!$B$37</f>
         <v>0</v>
       </c>
-      <c r="AO9" s="21">
-        <f>(AB9-Model!$B$7)*Model!$B$37</f>
+      <c r="AP9" s="21">
+        <f>(AC9-Model!$B$7)*Model!$B$38</f>
         <v>-0.29999999999999993</v>
       </c>
-      <c r="AP9" s="21">
-        <f>(AI9-Model!$B$8)*Model!$B$38</f>
+      <c r="AQ9" s="21">
+        <f>(AJ9-Model!$B$8)*Model!$B$39</f>
         <v>-2.4093333333333335</v>
       </c>
-      <c r="AQ9" s="21">
+      <c r="AR9" s="21">
         <f t="shared" si="1"/>
         <v>1.7406666666666659</v>
       </c>
     </row>
-    <row r="10" spans="1:43">
+    <row r="10" spans="1:44">
       <c r="A10" s="2" t="s">
         <v>62</v>
       </c>
@@ -2466,124 +2520,125 @@
         <v>-100</v>
       </c>
       <c r="J10" s="7"/>
-      <c r="K10" s="41">
+      <c r="K10" s="7"/>
+      <c r="L10" s="41">
         <v>4000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-2.5999999999999999E-2</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>59</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>57.5</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>0.3</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>0.5</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2.5</v>
       </c>
-      <c r="S10" s="13">
-        <f>MAX(MIN($L10*Model!$A$13+$M10,$N10)*$O10,0)</f>
+      <c r="T10" s="13">
+        <f>MAX(MIN($M10*Model!$A$13+$N10,$O10)*$P10,0)</f>
         <v>57.5</v>
       </c>
-      <c r="T10" s="13">
-        <f>MAX(MIN($L10*Model!$A$14+$M10,$N10)*$O10,0)</f>
+      <c r="U10" s="13">
+        <f>MAX(MIN($M10*Model!$A$14+$N10,$O10)*$P10,0)</f>
         <v>57.05</v>
       </c>
-      <c r="U10" s="13">
-        <f>MAX(MIN($L10*Model!$A$15+$M10,$N10)*$O10,0)</f>
+      <c r="V10" s="13">
+        <f>MAX(MIN($M10*Model!$A$15+$N10,$O10)*$P10,0)</f>
         <v>55.1</v>
       </c>
-      <c r="V10" s="13">
-        <f>MAX(MIN($L10*Model!$A$16+$M10,$N10)*$O10,0)</f>
+      <c r="W10" s="13">
+        <f>MAX(MIN($M10*Model!$A$16+$N10,$O10)*$P10,0)</f>
         <v>52.5</v>
       </c>
-      <c r="W10" s="13">
-        <f>MAX(MIN($L10*Model!$A$17+$M10,$N10)*$O10,0)</f>
+      <c r="X10" s="13">
+        <f>MAX(MIN($M10*Model!$A$17+$N10,$O10)*$P10,0)</f>
         <v>49.25</v>
       </c>
-      <c r="X10" s="13">
-        <f>MAX(MIN($L10*Model!$A$18+$M10,$N10)*$O10,0)</f>
+      <c r="Y10" s="13">
+        <f>MAX(MIN($M10*Model!$A$18+$N10,$O10)*$P10,0)</f>
         <v>48.6</v>
       </c>
-      <c r="Y10" s="13">
-        <f>MAX(MIN($L10*Model!$A$19+$M10,$N10)*$O10,0)</f>
+      <c r="Z10" s="13">
+        <f>MAX(MIN($M10*Model!$A$19+$N10,$O10)*$P10,0)</f>
         <v>46</v>
       </c>
-      <c r="Z10" s="13">
-        <f>S10*Model!$B$13+T10*Model!$B$14+U10*Model!$B$15+V10*Model!$B$16+W10*Model!$B$17+X10*Model!$B$18+Y10*Model!$B$19</f>
+      <c r="AA10" s="13">
+        <f>T10*Model!$B$13+U10*Model!$B$14+V10*Model!$B$15+W10*Model!$B$16+X10*Model!$B$17+Y10*Model!$B$18+Z10*Model!$B$19</f>
         <v>54.28</v>
       </c>
-      <c r="AA10" s="11">
+      <c r="AB10" s="11">
         <v>0.45</v>
       </c>
-      <c r="AB10" s="11">
+      <c r="AC10" s="11">
         <v>0.85</v>
       </c>
-      <c r="AC10" s="3" t="str">
+      <c r="AD10" s="3" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",AmmoChangeSheet[[#This Row],[pen_low]],";",AmmoChangeSheet[[#This Row],[pen_high]],";",AmmoChangeSheet[[#This Row],[pen_velocity_low]],";",AmmoChangeSheet[[#This Row],[pen_velocity_high]],")")</f>
         <v>stat(bullet_velocity;0.7;1.2;1500;3000)</v>
       </c>
-      <c r="AD10" s="11">
+      <c r="AE10" s="11">
         <v>0.7</v>
       </c>
-      <c r="AE10" s="11">
+      <c r="AF10" s="11">
         <v>1.2</v>
       </c>
-      <c r="AF10" s="15">
+      <c r="AG10" s="15">
         <v>1500</v>
       </c>
-      <c r="AG10" s="15">
+      <c r="AH10" s="15">
         <v>3000</v>
       </c>
-      <c r="AH10" s="16">
+      <c r="AI10" s="16">
         <f>Model!$B$4+IF(I10="",0,I10)</f>
         <v>2243</v>
       </c>
-      <c r="AI10" s="13">
+      <c r="AJ10" s="13">
         <f t="shared" si="0"/>
         <v>0.94766666666666666</v>
       </c>
-      <c r="AJ10" s="19">
+      <c r="AK10" s="19">
         <v>26</v>
       </c>
-      <c r="AK10" s="4" t="s">
+      <c r="AL10" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AL10" s="21">
-        <f>C10*Model!$B$24+D10*Model!$B$25+E10*Model!$B$26+F10*Model!$B$27+G10*Model!$B$28+H10*Model!$B$29+I10*Model!$B$30+J10*Model!$B$31+K10*Model!$B$32</f>
+      <c r="AM10" s="21">
+        <f>C10*Model!$B$24+D10*Model!$B$25+E10*Model!$B$26+F10*Model!$B$27+G10*Model!$B$28+H10*Model!$B$29+I10*Model!$B$30+J10*Model!$B$31+K10*Model!$B$32+L10*Model!$B$33</f>
         <v>-3.6000000000000005</v>
       </c>
-      <c r="AM10" s="21">
-        <f>(Z10-Model!$B$5)*Model!$B$35</f>
+      <c r="AN10" s="21">
+        <f>(AA10-Model!$B$5)*Model!$B$36</f>
         <v>6.4200000000000017</v>
       </c>
-      <c r="AN10" s="21">
-        <f>(Model!$B$6-AA10)*Model!$B$36</f>
+      <c r="AO10" s="21">
+        <f>(Model!$B$6-AB10)*Model!$B$37</f>
         <v>-0.20000000000000007</v>
       </c>
-      <c r="AO10" s="21">
-        <f>(AB10-Model!$B$7)*Model!$B$37</f>
+      <c r="AP10" s="21">
+        <f>(AC10-Model!$B$7)*Model!$B$38</f>
         <v>0</v>
       </c>
-      <c r="AP10" s="21">
-        <f>(AI10-Model!$B$8)*Model!$B$38</f>
+      <c r="AQ10" s="21">
+        <f>(AJ10-Model!$B$8)*Model!$B$39</f>
         <v>-0.20933333333333337</v>
       </c>
-      <c r="AQ10" s="21">
+      <c r="AR10" s="21">
         <f t="shared" si="1"/>
         <v>2.4106666666666676</v>
       </c>
     </row>
-    <row r="11" spans="1:43">
+    <row r="11" spans="1:44">
       <c r="A11" s="2" t="s">
         <v>64</v>
       </c>
@@ -2610,124 +2665,125 @@
         <v>-100</v>
       </c>
       <c r="J11" s="7"/>
-      <c r="K11" s="41">
+      <c r="K11" s="7"/>
+      <c r="L11" s="41">
         <v>4000</v>
       </c>
-      <c r="L11" s="3">
+      <c r="M11" s="3">
         <v>-2.1999999999999999E-2</v>
       </c>
-      <c r="M11" s="3">
+      <c r="N11" s="3">
         <v>57</v>
       </c>
-      <c r="N11" s="3">
+      <c r="O11" s="3">
         <v>55</v>
       </c>
-      <c r="O11" s="3">
+      <c r="P11" s="3">
         <v>1</v>
       </c>
-      <c r="P11" s="3">
+      <c r="Q11" s="3">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="R11" s="3">
         <v>0.4</v>
       </c>
-      <c r="R11" s="3">
+      <c r="S11" s="3">
         <v>2.5</v>
       </c>
-      <c r="S11" s="13">
-        <f>MAX(MIN($L11*Model!$A$13+$M11,$N11)*$O11,0)</f>
+      <c r="T11" s="13">
+        <f>MAX(MIN($M11*Model!$A$13+$N11,$O11)*$P11,0)</f>
         <v>55</v>
       </c>
-      <c r="T11" s="13">
-        <f>MAX(MIN($L11*Model!$A$14+$M11,$N11)*$O11,0)</f>
+      <c r="U11" s="13">
+        <f>MAX(MIN($M11*Model!$A$14+$N11,$O11)*$P11,0)</f>
         <v>55</v>
       </c>
-      <c r="U11" s="13">
-        <f>MAX(MIN($L11*Model!$A$15+$M11,$N11)*$O11,0)</f>
+      <c r="V11" s="13">
+        <f>MAX(MIN($M11*Model!$A$15+$N11,$O11)*$P11,0)</f>
         <v>53.7</v>
       </c>
-      <c r="V11" s="13">
-        <f>MAX(MIN($L11*Model!$A$16+$M11,$N11)*$O11,0)</f>
+      <c r="W11" s="13">
+        <f>MAX(MIN($M11*Model!$A$16+$N11,$O11)*$P11,0)</f>
         <v>51.5</v>
       </c>
-      <c r="W11" s="13">
-        <f>MAX(MIN($L11*Model!$A$17+$M11,$N11)*$O11,0)</f>
+      <c r="X11" s="13">
+        <f>MAX(MIN($M11*Model!$A$17+$N11,$O11)*$P11,0)</f>
         <v>48.75</v>
       </c>
-      <c r="X11" s="13">
-        <f>MAX(MIN($L11*Model!$A$18+$M11,$N11)*$O11,0)</f>
+      <c r="Y11" s="13">
+        <f>MAX(MIN($M11*Model!$A$18+$N11,$O11)*$P11,0)</f>
         <v>48.2</v>
       </c>
-      <c r="Y11" s="13">
-        <f>MAX(MIN($L11*Model!$A$19+$M11,$N11)*$O11,0)</f>
+      <c r="Z11" s="13">
+        <f>MAX(MIN($M11*Model!$A$19+$N11,$O11)*$P11,0)</f>
         <v>46</v>
       </c>
-      <c r="Z11" s="13">
-        <f>S11*Model!$B$13+T11*Model!$B$14+U11*Model!$B$15+V11*Model!$B$16+W11*Model!$B$17+X11*Model!$B$18+Y11*Model!$B$19</f>
+      <c r="AA11" s="13">
+        <f>T11*Model!$B$13+U11*Model!$B$14+V11*Model!$B$15+W11*Model!$B$16+X11*Model!$B$17+Y11*Model!$B$18+Z11*Model!$B$19</f>
         <v>52.790000000000006</v>
       </c>
-      <c r="AA11" s="11">
+      <c r="AB11" s="11">
         <v>0.4</v>
       </c>
-      <c r="AB11" s="11">
+      <c r="AC11" s="11">
         <v>0.8</v>
       </c>
-      <c r="AC11" s="3" t="str">
+      <c r="AD11" s="3" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",AmmoChangeSheet[[#This Row],[pen_low]],";",AmmoChangeSheet[[#This Row],[pen_high]],";",AmmoChangeSheet[[#This Row],[pen_velocity_low]],";",AmmoChangeSheet[[#This Row],[pen_velocity_high]],")")</f>
         <v>stat(bullet_velocity;1.05;1.55;1500;3000)</v>
       </c>
-      <c r="AD11" s="11">
+      <c r="AE11" s="11">
         <v>1.05</v>
       </c>
-      <c r="AE11" s="11">
+      <c r="AF11" s="11">
         <v>1.55</v>
       </c>
-      <c r="AF11" s="15">
+      <c r="AG11" s="15">
         <v>1500</v>
       </c>
-      <c r="AG11" s="15">
+      <c r="AH11" s="15">
         <v>3000</v>
       </c>
-      <c r="AH11" s="16">
+      <c r="AI11" s="16">
         <f>Model!$B$4+IF(I11="",0,I11)</f>
         <v>2243</v>
       </c>
-      <c r="AI11" s="13">
+      <c r="AJ11" s="13">
         <f t="shared" si="0"/>
         <v>1.2976666666666667</v>
       </c>
-      <c r="AJ11" s="19">
+      <c r="AK11" s="19">
         <v>24</v>
       </c>
-      <c r="AK11" s="4" t="s">
+      <c r="AL11" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AL11" s="21">
-        <f>C11*Model!$B$24+D11*Model!$B$25+E11*Model!$B$26+F11*Model!$B$27+G11*Model!$B$28+H11*Model!$B$29+I11*Model!$B$30+J11*Model!$B$31+K11*Model!$B$32</f>
+      <c r="AM11" s="21">
+        <f>C11*Model!$B$24+D11*Model!$B$25+E11*Model!$B$26+F11*Model!$B$27+G11*Model!$B$28+H11*Model!$B$29+I11*Model!$B$30+J11*Model!$B$31+K11*Model!$B$32+L11*Model!$B$33</f>
         <v>-2.9000000000000004</v>
       </c>
-      <c r="AM11" s="21">
-        <f>(Z11-Model!$B$5)*Model!$B$35</f>
+      <c r="AN11" s="21">
+        <f>(AA11-Model!$B$5)*Model!$B$36</f>
         <v>4.1850000000000094</v>
       </c>
-      <c r="AN11" s="21">
-        <f>(Model!$B$6-AA11)*Model!$B$36</f>
+      <c r="AO11" s="21">
+        <f>(Model!$B$6-AB11)*Model!$B$37</f>
         <v>-0.10000000000000009</v>
       </c>
-      <c r="AO11" s="21">
-        <f>(AB11-Model!$B$7)*Model!$B$37</f>
+      <c r="AP11" s="21">
+        <f>(AC11-Model!$B$7)*Model!$B$38</f>
         <v>-0.1499999999999998</v>
       </c>
-      <c r="AP11" s="21">
-        <f>(AI11-Model!$B$8)*Model!$B$38</f>
+      <c r="AQ11" s="21">
+        <f>(AJ11-Model!$B$8)*Model!$B$39</f>
         <v>1.190666666666667</v>
       </c>
-      <c r="AQ11" s="21">
+      <c r="AR11" s="21">
         <f t="shared" si="1"/>
         <v>2.225666666666676</v>
       </c>
     </row>
-    <row r="12" spans="1:43">
+    <row r="12" spans="1:44">
       <c r="A12" s="5" t="s">
         <v>66</v>
       </c>
@@ -2756,135 +2812,138 @@
       <c r="J12" s="8">
         <v>-0.02</v>
       </c>
-      <c r="K12" s="42">
+      <c r="K12" s="8">
+        <v>-0.7</v>
+      </c>
+      <c r="L12" s="42">
         <v>2000</v>
       </c>
-      <c r="L12" s="43">
+      <c r="M12" s="43">
         <v>-6.6000000000000003E-2</v>
-      </c>
-      <c r="M12" s="43">
-        <v>65</v>
       </c>
       <c r="N12" s="43">
         <v>65</v>
       </c>
       <c r="O12" s="43">
+        <v>65</v>
+      </c>
+      <c r="P12" s="43">
         <v>1</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>0.3</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>0.5</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2.5</v>
       </c>
-      <c r="S12" s="14">
-        <f>MAX(MIN($L12*Model!$A$13+$M12,$N12)*$O12,0)</f>
+      <c r="T12" s="14">
+        <f>MAX(MIN($M12*Model!$A$13+$N12,$O12)*$P12,0)</f>
         <v>63.35</v>
       </c>
-      <c r="T12" s="14">
-        <f>MAX(MIN($L12*Model!$A$14+$M12,$N12)*$O12,0)</f>
+      <c r="U12" s="14">
+        <f>MAX(MIN($M12*Model!$A$14+$N12,$O12)*$P12,0)</f>
         <v>60.05</v>
       </c>
-      <c r="U12" s="14">
-        <f>MAX(MIN($L12*Model!$A$15+$M12,$N12)*$O12,0)</f>
+      <c r="V12" s="14">
+        <f>MAX(MIN($M12*Model!$A$15+$N12,$O12)*$P12,0)</f>
         <v>55.1</v>
       </c>
-      <c r="V12" s="14">
-        <f>MAX(MIN($L12*Model!$A$16+$M12,$N12)*$O12,0)</f>
+      <c r="W12" s="14">
+        <f>MAX(MIN($M12*Model!$A$16+$N12,$O12)*$P12,0)</f>
         <v>48.5</v>
       </c>
-      <c r="W12" s="14">
-        <f>MAX(MIN($L12*Model!$A$17+$M12,$N12)*$O12,0)</f>
+      <c r="X12" s="14">
+        <f>MAX(MIN($M12*Model!$A$17+$N12,$O12)*$P12,0)</f>
         <v>40.25</v>
       </c>
-      <c r="X12" s="14">
-        <f>MAX(MIN($L12*Model!$A$18+$M12,$N12)*$O12,0)</f>
+      <c r="Y12" s="14">
+        <f>MAX(MIN($M12*Model!$A$18+$N12,$O12)*$P12,0)</f>
         <v>38.599999999999994</v>
       </c>
-      <c r="Y12" s="14">
-        <f>MAX(MIN($L12*Model!$A$19+$M12,$N12)*$O12,0)</f>
+      <c r="Z12" s="14">
+        <f>MAX(MIN($M12*Model!$A$19+$N12,$O12)*$P12,0)</f>
         <v>32</v>
       </c>
-      <c r="Z12" s="14">
-        <f>S12*Model!$B$13+T12*Model!$B$14+U12*Model!$B$15+V12*Model!$B$16+W12*Model!$B$17+X12*Model!$B$18+Y12*Model!$B$19</f>
+      <c r="AA12" s="14">
+        <f>T12*Model!$B$13+U12*Model!$B$14+V12*Model!$B$15+W12*Model!$B$16+X12*Model!$B$17+Y12*Model!$B$18+Z12*Model!$B$19</f>
         <v>53.45</v>
       </c>
-      <c r="AA12" s="12">
+      <c r="AB12" s="12">
         <v>0.75</v>
       </c>
-      <c r="AB12" s="12">
+      <c r="AC12" s="12">
         <v>0.25</v>
       </c>
-      <c r="AC12" s="3" t="str">
+      <c r="AD12" s="3" t="str">
         <f>_xlfn.CONCAT("stat(bullet_velocity;",AmmoChangeSheet[[#This Row],[pen_low]],";",AmmoChangeSheet[[#This Row],[pen_high]],";",AmmoChangeSheet[[#This Row],[pen_velocity_low]],";",AmmoChangeSheet[[#This Row],[pen_velocity_high]],")")</f>
         <v>stat(bullet_velocity;0;0.5;500;2000)</v>
       </c>
-      <c r="AD12" s="12">
+      <c r="AE12" s="12">
         <v>0</v>
       </c>
-      <c r="AE12" s="12">
+      <c r="AF12" s="12">
         <v>0.5</v>
       </c>
-      <c r="AF12" s="17">
+      <c r="AG12" s="17">
         <v>500</v>
       </c>
-      <c r="AG12" s="17">
+      <c r="AH12" s="17">
         <v>2000</v>
       </c>
-      <c r="AH12" s="18">
+      <c r="AI12" s="18">
         <f>Model!$B$4+IF(I12="",0,I12)</f>
         <v>1143</v>
       </c>
-      <c r="AI12" s="14">
+      <c r="AJ12" s="14">
         <f t="shared" si="0"/>
         <v>0.21433333333333332</v>
       </c>
-      <c r="AJ12" s="20">
+      <c r="AK12" s="20">
         <v>23</v>
       </c>
-      <c r="AK12" s="6" t="s">
+      <c r="AL12" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AL12" s="22">
-        <f>C12*Model!$B$24+D12*Model!$B$25+E12*Model!$B$26+F12*Model!$B$27+G12*Model!$B$28+H12*Model!$B$29+I12*Model!$B$30+J12*Model!$B$31+K12*Model!$B$32</f>
-        <v>-4.3</v>
-      </c>
-      <c r="AM12" s="22">
-        <f>(Z12-Model!$B$5)*Model!$B$35</f>
+      <c r="AM12" s="21">
+        <f>C12*Model!$B$24+D12*Model!$B$25+E12*Model!$B$26+F12*Model!$B$27+G12*Model!$B$28+H12*Model!$B$29+I12*Model!$B$30+J12*Model!$B$31+K12*Model!$B$32+L12*Model!$B$33</f>
+        <v>2.7</v>
+      </c>
+      <c r="AN12" s="22">
+        <f>(AA12-Model!$B$5)*Model!$B$36</f>
         <v>5.1750000000000043</v>
       </c>
-      <c r="AN12" s="22">
-        <f>(Model!$B$6-AA12)*Model!$B$36</f>
+      <c r="AO12" s="22">
+        <f>(Model!$B$6-AB12)*Model!$B$37</f>
         <v>-0.8</v>
       </c>
-      <c r="AO12" s="22">
-        <f>(AB12-Model!$B$7)*Model!$B$37</f>
+      <c r="AP12" s="22">
+        <f>(AC12-Model!$B$7)*Model!$B$38</f>
         <v>-1.7999999999999998</v>
       </c>
-      <c r="AP12" s="22">
-        <f>(AI12-Model!$B$8)*Model!$B$38</f>
+      <c r="AQ12" s="22">
+        <f>(AJ12-Model!$B$8)*Model!$B$39</f>
         <v>-3.1426666666666669</v>
       </c>
-      <c r="AQ12" s="22">
+      <c r="AR12" s="22">
         <f t="shared" si="1"/>
-        <v>-4.8676666666666621</v>
+        <v>2.1323333333333379</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="AL1:AQ1"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="L1:O1"/>
-    <mergeCell ref="S1:Z1"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="AM1:AR1"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="T1:AA1"/>
+    <mergeCell ref="AB1:AH1"/>
+    <mergeCell ref="AI1:AJ1"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
-  <conditionalFormatting sqref="AQ3:AQ12">
+  <conditionalFormatting sqref="AR3:AR12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -2907,7 +2966,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3222,68 +3281,77 @@
     </row>
     <row r="32" spans="1:3" ht="15">
       <c r="A32" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="B32" s="32">
+        <v>-10</v>
+      </c>
+      <c r="C32" s="30"/>
+    </row>
+    <row r="33" spans="1:3" ht="15">
+      <c r="A33" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="B32" s="32">
+      <c r="B33" s="32">
         <v>0</v>
       </c>
-      <c r="C32" s="30" t="s">
+      <c r="C33" s="30" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15">
-      <c r="A33" s="27"/>
-      <c r="B33" s="33"/>
-      <c r="C33" s="27"/>
-    </row>
     <row r="34" spans="1:3" ht="15">
-      <c r="A34" s="52" t="s">
+      <c r="A34" s="27"/>
+      <c r="B34" s="33"/>
+      <c r="C34" s="27"/>
+    </row>
+    <row r="35" spans="1:3" ht="15">
+      <c r="A35" s="52" t="s">
         <v>97</v>
       </c>
-      <c r="B34" s="53"/>
-      <c r="C34" s="52"/>
-    </row>
-    <row r="35" spans="1:3" ht="15">
-      <c r="A35" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="B35" s="35">
-        <v>1.5</v>
-      </c>
-      <c r="C35" s="34" t="s">
-        <v>98</v>
-      </c>
+      <c r="B35" s="53"/>
+      <c r="C35" s="52"/>
     </row>
     <row r="36" spans="1:3" ht="15">
       <c r="A36" s="34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B36" s="35">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="C36" s="34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15">
       <c r="A37" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" s="35">
+        <v>2</v>
+      </c>
+      <c r="C37" s="34" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="15">
+      <c r="A38" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="35">
+      <c r="B38" s="35">
         <v>3</v>
       </c>
-      <c r="C37" s="34" t="s">
+      <c r="C38" s="34" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15">
-      <c r="A38" s="36" t="s">
+    <row r="39" spans="1:3" ht="15">
+      <c r="A39" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="37">
+      <c r="B39" s="37">
         <v>4</v>
       </c>
-      <c r="C38" s="36" t="s">
+      <c r="C39" s="36" t="s">
         <v>100</v>
       </c>
     </row>
@@ -3292,7 +3360,7 @@
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/changes/545-ammo-super.xlsx
+++ b/changes/545-ammo-super.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-balancing\changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66AE15E-29D9-48AB-91D6-6706B5F73042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F1C9E5-6A6E-4729-B239-AFD91166DF1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -711,43 +711,6 @@
         <name val="Aptos"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFEAF3F8"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color rgb="FFD8E0E7"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD8E0E7"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF1F2933"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -854,6 +817,43 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF1F2933"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEAF3F8"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD8E0E7"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD8E0E7"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -1010,15 +1010,15 @@
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="bullet_damage"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="bullet_velocity" dataDxfId="10"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="fire_rate" dataDxfId="9"/>
-    <tableColumn id="41" xr3:uid="{D6CEC36C-985A-453A-AC8C-074C80CDE463}" name="muzzle_loudness" dataDxfId="0"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="price" dataDxfId="8"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="damage_torso_a" dataDxfId="7"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="damage_torso_b" dataDxfId="6"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="damage_torso_c" dataDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="damage_torso_d" dataDxfId="4"/>
-    <tableColumn id="43" xr3:uid="{D5021237-E759-4A3A-B219-A4E638DB2DAD}" name="damage_arm_d" dataDxfId="3"/>
-    <tableColumn id="45" xr3:uid="{55603E35-2152-4FD3-9598-9256E449C5B0}" name="damage_leg_d" dataDxfId="2"/>
-    <tableColumn id="44" xr3:uid="{8CA87E20-CD33-48FB-A112-3BC0E2D56BD8}" name="damage_head_d" dataDxfId="1"/>
+    <tableColumn id="41" xr3:uid="{D6CEC36C-985A-453A-AC8C-074C80CDE463}" name="muzzle_loudness" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="price" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="damage_torso_a" dataDxfId="6"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="damage_torso_b" dataDxfId="5"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="damage_torso_c" dataDxfId="4"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="damage_torso_d" dataDxfId="3"/>
+    <tableColumn id="43" xr3:uid="{D5021237-E759-4A3A-B219-A4E638DB2DAD}" name="damage_arm_d" dataDxfId="2"/>
+    <tableColumn id="45" xr3:uid="{55603E35-2152-4FD3-9598-9256E449C5B0}" name="damage_leg_d" dataDxfId="1"/>
+    <tableColumn id="44" xr3:uid="{8CA87E20-CD33-48FB-A112-3BC0E2D56BD8}" name="damage_head_d" dataDxfId="0"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="damage_25"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="damage_75"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="damage_150"/>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="AO3" s="21">
         <f>(Model!$B$6-AB3)*Model!$B$37</f>
-        <v>-0.30000000000000004</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AP3" s="21">
         <f>(AC3-Model!$B$7)*Model!$B$38</f>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="AR3" s="21">
         <f t="shared" ref="AR3:AR12" si="1">SUM(AM3:AQ3)</f>
-        <v>-0.30099999999999572</v>
+        <v>0.29900000000000437</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AO4" s="21">
         <f>(Model!$B$6-AB4)*Model!$B$37</f>
-        <v>-0.40000000000000013</v>
+        <v>0.40000000000000013</v>
       </c>
       <c r="AP4" s="21">
         <f>(AC4-Model!$B$7)*Model!$B$38</f>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="AR4" s="21">
         <f t="shared" si="1"/>
-        <v>0.73233333333333572</v>
+        <v>1.5323333333333355</v>
       </c>
     </row>
     <row r="5" spans="1:44">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="AO5" s="21">
         <f>(Model!$B$6-AB5)*Model!$B$37</f>
-        <v>-0.20000000000000007</v>
+        <v>0.20000000000000007</v>
       </c>
       <c r="AP5" s="21">
         <f>(AC5-Model!$B$7)*Model!$B$38</f>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AR5" s="21">
         <f t="shared" si="1"/>
-        <v>-0.1843333333333268</v>
+        <v>0.21566666666667356</v>
       </c>
     </row>
     <row r="6" spans="1:44">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AO6" s="21">
         <f>(Model!$B$6-AB6)*Model!$B$37</f>
-        <v>-0.20000000000000007</v>
+        <v>0.20000000000000007</v>
       </c>
       <c r="AP6" s="21">
         <f>(AC6-Model!$B$7)*Model!$B$38</f>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AR6" s="21">
         <f t="shared" si="1"/>
-        <v>0.10566666666667868</v>
+        <v>0.50566666666667881</v>
       </c>
     </row>
     <row r="7" spans="1:44">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="AO7" s="21">
         <f>(Model!$B$6-AB7)*Model!$B$37</f>
-        <v>-0.40000000000000013</v>
+        <v>0.40000000000000013</v>
       </c>
       <c r="AP7" s="21">
         <f>(AC7-Model!$B$7)*Model!$B$38</f>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="AR7" s="21">
         <f t="shared" si="1"/>
-        <v>1.029000000000015</v>
+        <v>1.8290000000000157</v>
       </c>
     </row>
     <row r="8" spans="1:44">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="AO8" s="21">
         <f>(Model!$B$6-AB8)*Model!$B$37</f>
-        <v>-0.10000000000000009</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AP8" s="21">
         <f>(AC8-Model!$B$7)*Model!$B$38</f>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AR8" s="21">
         <f t="shared" si="1"/>
-        <v>1.0156666666666703</v>
+        <v>1.2156666666666704</v>
       </c>
     </row>
     <row r="9" spans="1:44">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="AO10" s="21">
         <f>(Model!$B$6-AB10)*Model!$B$37</f>
-        <v>-0.20000000000000007</v>
+        <v>0.20000000000000007</v>
       </c>
       <c r="AP10" s="21">
         <f>(AC10-Model!$B$7)*Model!$B$38</f>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AR10" s="21">
         <f t="shared" si="1"/>
-        <v>2.4106666666666676</v>
+        <v>2.810666666666668</v>
       </c>
     </row>
     <row r="11" spans="1:44">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="AO11" s="21">
         <f>(Model!$B$6-AB11)*Model!$B$37</f>
-        <v>-0.10000000000000009</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AP11" s="21">
         <f>(AC11-Model!$B$7)*Model!$B$38</f>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="AR11" s="21">
         <f t="shared" si="1"/>
-        <v>2.225666666666676</v>
+        <v>2.4256666666666762</v>
       </c>
     </row>
     <row r="12" spans="1:44">
@@ -2813,7 +2813,7 @@
         <v>-0.02</v>
       </c>
       <c r="K12" s="8">
-        <v>-0.7</v>
+        <v>-0.6</v>
       </c>
       <c r="L12" s="42">
         <v>2000</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="AM12" s="21">
         <f>C12*Model!$B$24+D12*Model!$B$25+E12*Model!$B$26+F12*Model!$B$27+G12*Model!$B$28+H12*Model!$B$29+I12*Model!$B$30+J12*Model!$B$31+K12*Model!$B$32+L12*Model!$B$33</f>
-        <v>2.7</v>
+        <v>-1.2999999999999998</v>
       </c>
       <c r="AN12" s="22">
         <f>(AA12-Model!$B$5)*Model!$B$36</f>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AO12" s="22">
         <f>(Model!$B$6-AB12)*Model!$B$37</f>
-        <v>-0.8</v>
+        <v>0.8</v>
       </c>
       <c r="AP12" s="22">
         <f>(AC12-Model!$B$7)*Model!$B$38</f>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="AR12" s="22">
         <f t="shared" si="1"/>
-        <v>2.1323333333333379</v>
+        <v>-0.2676666666666625</v>
       </c>
     </row>
   </sheetData>
@@ -3284,7 +3284,7 @@
         <v>104</v>
       </c>
       <c r="B32" s="32">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="C32" s="30"/>
     </row>
@@ -3327,7 +3327,7 @@
         <v>30</v>
       </c>
       <c r="B37" s="35">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="C37" s="34" t="s">
         <v>99</v>

--- a/changes/545-ammo-super.xlsx
+++ b/changes/545-ammo-super.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-balancing\changes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yifan/Documents/deadline-dev/deadline-balancing/changes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F1C9E5-6A6E-4729-B239-AFD91166DF1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0198D628-CCC8-B24B-8214-A990DDE178F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="545-ammo" sheetId="1" r:id="rId1"/>
@@ -1271,17 +1271,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AR12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="26.125" customWidth="1"/>
-    <col min="2" max="2" width="22.75" customWidth="1"/>
-    <col min="3" max="8" width="5.625" customWidth="1"/>
+    <col min="1" max="1" width="26.1640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="3" max="8" width="5.6640625" customWidth="1"/>
     <col min="9" max="9" width="8" customWidth="1"/>
-    <col min="10" max="29" width="5.625" customWidth="1"/>
-    <col min="30" max="30" width="27.125" customWidth="1"/>
-    <col min="31" max="37" width="5.625" customWidth="1"/>
-    <col min="38" max="38" width="9.625" customWidth="1"/>
-    <col min="39" max="44" width="5.625" customWidth="1"/>
+    <col min="10" max="29" width="5.6640625" customWidth="1"/>
+    <col min="30" max="30" width="27.1640625" customWidth="1"/>
+    <col min="31" max="37" width="5.6640625" customWidth="1"/>
+    <col min="38" max="38" width="9.6640625" customWidth="1"/>
+    <col min="39" max="44" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="24" customHeight="1">
@@ -1344,7 +1344,7 @@
       <c r="AQ1" s="46"/>
       <c r="AR1" s="46"/>
     </row>
-    <row r="2" spans="1:44" ht="45.95" customHeight="1">
+    <row r="2" spans="1:44" ht="46" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:44">
+    <row r="3" spans="1:44" ht="15">
       <c r="A3" s="2" t="s">
         <v>47</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>0.29900000000000437</v>
       </c>
     </row>
-    <row r="4" spans="1:44">
+    <row r="4" spans="1:44" ht="15">
       <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>1.5323333333333355</v>
       </c>
     </row>
-    <row r="5" spans="1:44">
+    <row r="5" spans="1:44" ht="15">
       <c r="A5" s="2" t="s">
         <v>52</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>0.21566666666667356</v>
       </c>
     </row>
-    <row r="6" spans="1:44">
+    <row r="6" spans="1:44" ht="15">
       <c r="A6" s="2" t="s">
         <v>54</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>0.50566666666667881</v>
       </c>
     </row>
-    <row r="7" spans="1:44">
+    <row r="7" spans="1:44" ht="15">
       <c r="A7" s="2" t="s">
         <v>56</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>1.8290000000000157</v>
       </c>
     </row>
-    <row r="8" spans="1:44">
+    <row r="8" spans="1:44" ht="15">
       <c r="A8" s="2" t="s">
         <v>58</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>1.2156666666666704</v>
       </c>
     </row>
-    <row r="9" spans="1:44">
+    <row r="9" spans="1:44" ht="15">
       <c r="A9" s="2" t="s">
         <v>60</v>
       </c>
@@ -2493,7 +2493,7 @@
         <v>1.7406666666666659</v>
       </c>
     </row>
-    <row r="10" spans="1:44">
+    <row r="10" spans="1:44" ht="15">
       <c r="A10" s="2" t="s">
         <v>62</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>2.810666666666668</v>
       </c>
     </row>
-    <row r="11" spans="1:44">
+    <row r="11" spans="1:44" ht="15">
       <c r="A11" s="2" t="s">
         <v>64</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>2.4256666666666762</v>
       </c>
     </row>
-    <row r="12" spans="1:44">
+    <row r="12" spans="1:44" ht="15">
       <c r="A12" s="5" t="s">
         <v>66</v>
       </c>
@@ -2797,29 +2797,29 @@
         <v>0.1</v>
       </c>
       <c r="E12" s="39">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="F12" s="39">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G12" s="8">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="H12" s="10"/>
       <c r="I12" s="39">
-        <v>-1200</v>
+        <v>-1100</v>
       </c>
       <c r="J12" s="8">
         <v>-0.02</v>
       </c>
       <c r="K12" s="8">
-        <v>-0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="L12" s="42">
         <v>2000</v>
       </c>
       <c r="M12" s="43">
-        <v>-6.6000000000000003E-2</v>
+        <v>-6.4000000000000001E-2</v>
       </c>
       <c r="N12" s="43">
         <v>65</v>
@@ -2841,35 +2841,35 @@
       </c>
       <c r="T12" s="14">
         <f>MAX(MIN($M12*Model!$A$13+$N12,$O12)*$P12,0)</f>
-        <v>63.35</v>
+        <v>63.4</v>
       </c>
       <c r="U12" s="14">
         <f>MAX(MIN($M12*Model!$A$14+$N12,$O12)*$P12,0)</f>
-        <v>60.05</v>
+        <v>60.2</v>
       </c>
       <c r="V12" s="14">
         <f>MAX(MIN($M12*Model!$A$15+$N12,$O12)*$P12,0)</f>
-        <v>55.1</v>
+        <v>55.4</v>
       </c>
       <c r="W12" s="14">
         <f>MAX(MIN($M12*Model!$A$16+$N12,$O12)*$P12,0)</f>
-        <v>48.5</v>
+        <v>49</v>
       </c>
       <c r="X12" s="14">
         <f>MAX(MIN($M12*Model!$A$17+$N12,$O12)*$P12,0)</f>
-        <v>40.25</v>
+        <v>41</v>
       </c>
       <c r="Y12" s="14">
         <f>MAX(MIN($M12*Model!$A$18+$N12,$O12)*$P12,0)</f>
-        <v>38.599999999999994</v>
+        <v>39.4</v>
       </c>
       <c r="Z12" s="14">
         <f>MAX(MIN($M12*Model!$A$19+$N12,$O12)*$P12,0)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AA12" s="14">
         <f>T12*Model!$B$13+U12*Model!$B$14+V12*Model!$B$15+W12*Model!$B$16+X12*Model!$B$17+Y12*Model!$B$18+Z12*Model!$B$19</f>
-        <v>53.45</v>
+        <v>53.8</v>
       </c>
       <c r="AB12" s="12">
         <v>0.75</v>
@@ -2895,11 +2895,11 @@
       </c>
       <c r="AI12" s="18">
         <f>Model!$B$4+IF(I12="",0,I12)</f>
-        <v>1143</v>
+        <v>1243</v>
       </c>
       <c r="AJ12" s="14">
         <f t="shared" si="0"/>
-        <v>0.21433333333333332</v>
+        <v>0.24766666666666667</v>
       </c>
       <c r="AK12" s="20">
         <v>23</v>
@@ -2909,11 +2909,11 @@
       </c>
       <c r="AM12" s="21">
         <f>C12*Model!$B$24+D12*Model!$B$25+E12*Model!$B$26+F12*Model!$B$27+G12*Model!$B$28+H12*Model!$B$29+I12*Model!$B$30+J12*Model!$B$31+K12*Model!$B$32+L12*Model!$B$33</f>
-        <v>-1.2999999999999998</v>
+        <v>2.3999999999999995</v>
       </c>
       <c r="AN12" s="22">
         <f>(AA12-Model!$B$5)*Model!$B$36</f>
-        <v>5.1750000000000043</v>
+        <v>5.6999999999999957</v>
       </c>
       <c r="AO12" s="22">
         <f>(Model!$B$6-AB12)*Model!$B$37</f>
@@ -2925,11 +2925,11 @@
       </c>
       <c r="AQ12" s="22">
         <f>(AJ12-Model!$B$8)*Model!$B$39</f>
-        <v>-3.1426666666666669</v>
+        <v>-3.0093333333333332</v>
       </c>
       <c r="AR12" s="22">
         <f t="shared" si="1"/>
-        <v>-0.2676666666666625</v>
+        <v>4.090666666666662</v>
       </c>
     </row>
   </sheetData>
@@ -2967,14 +2967,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="32.1" customHeight="1">
+    <row r="1" spans="1:3" ht="32" customHeight="1">
       <c r="A1" s="51" t="s">
         <v>68</v>
       </c>

--- a/changes/545-ammo-super.xlsx
+++ b/changes/545-ammo-super.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yifan/Documents/deadline-dev/deadline-balancing/changes/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-dev\deadline-balancing\changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0198D628-CCC8-B24B-8214-A990DDE178F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E769039E-3F7B-40A0-9791-2D28BEB2E707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="545-ammo" sheetId="1" r:id="rId1"/>
@@ -1271,17 +1271,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AR12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="26.1640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="8" width="5.6640625" customWidth="1"/>
+    <col min="1" max="1" width="26.125" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="8" width="5.625" customWidth="1"/>
     <col min="9" max="9" width="8" customWidth="1"/>
-    <col min="10" max="29" width="5.6640625" customWidth="1"/>
-    <col min="30" max="30" width="27.1640625" customWidth="1"/>
-    <col min="31" max="37" width="5.6640625" customWidth="1"/>
-    <col min="38" max="38" width="9.6640625" customWidth="1"/>
-    <col min="39" max="44" width="5.6640625" customWidth="1"/>
+    <col min="10" max="29" width="5.625" customWidth="1"/>
+    <col min="30" max="30" width="27.125" customWidth="1"/>
+    <col min="31" max="37" width="5.625" customWidth="1"/>
+    <col min="38" max="38" width="9.625" customWidth="1"/>
+    <col min="39" max="44" width="5.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="24" customHeight="1">
@@ -1344,7 +1344,7 @@
       <c r="AQ1" s="46"/>
       <c r="AR1" s="46"/>
     </row>
-    <row r="2" spans="1:44" ht="46" customHeight="1">
+    <row r="2" spans="1:44" ht="45.95" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:44" ht="15">
+    <row r="3" spans="1:44">
       <c r="A3" s="2" t="s">
         <v>47</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>0.29900000000000437</v>
       </c>
     </row>
-    <row r="4" spans="1:44" ht="15">
+    <row r="4" spans="1:44">
       <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>1.5323333333333355</v>
       </c>
     </row>
-    <row r="5" spans="1:44" ht="15">
+    <row r="5" spans="1:44">
       <c r="A5" s="2" t="s">
         <v>52</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>0.21566666666667356</v>
       </c>
     </row>
-    <row r="6" spans="1:44" ht="15">
+    <row r="6" spans="1:44">
       <c r="A6" s="2" t="s">
         <v>54</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>0.50566666666667881</v>
       </c>
     </row>
-    <row r="7" spans="1:44" ht="15">
+    <row r="7" spans="1:44">
       <c r="A7" s="2" t="s">
         <v>56</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>1.8290000000000157</v>
       </c>
     </row>
-    <row r="8" spans="1:44" ht="15">
+    <row r="8" spans="1:44">
       <c r="A8" s="2" t="s">
         <v>58</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>1.2156666666666704</v>
       </c>
     </row>
-    <row r="9" spans="1:44" ht="15">
+    <row r="9" spans="1:44">
       <c r="A9" s="2" t="s">
         <v>60</v>
       </c>
@@ -2493,7 +2493,7 @@
         <v>1.7406666666666659</v>
       </c>
     </row>
-    <row r="10" spans="1:44" ht="15">
+    <row r="10" spans="1:44">
       <c r="A10" s="2" t="s">
         <v>62</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>2.810666666666668</v>
       </c>
     </row>
-    <row r="11" spans="1:44" ht="15">
+    <row r="11" spans="1:44">
       <c r="A11" s="2" t="s">
         <v>64</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>2.4256666666666762</v>
       </c>
     </row>
-    <row r="12" spans="1:44" ht="15">
+    <row r="12" spans="1:44">
       <c r="A12" s="5" t="s">
         <v>66</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>-0.02</v>
       </c>
       <c r="K12" s="8">
-        <v>-0.7</v>
+        <v>-0.65</v>
       </c>
       <c r="L12" s="42">
         <v>2000</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="AM12" s="21">
         <f>C12*Model!$B$24+D12*Model!$B$25+E12*Model!$B$26+F12*Model!$B$27+G12*Model!$B$28+H12*Model!$B$29+I12*Model!$B$30+J12*Model!$B$31+K12*Model!$B$32+L12*Model!$B$33</f>
-        <v>2.3999999999999995</v>
+        <v>2.1499999999999995</v>
       </c>
       <c r="AN12" s="22">
         <f>(AA12-Model!$B$5)*Model!$B$36</f>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="AR12" s="22">
         <f t="shared" si="1"/>
-        <v>4.090666666666662</v>
+        <v>3.840666666666662</v>
       </c>
     </row>
   </sheetData>
@@ -2967,14 +2967,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="32" customHeight="1">
+    <row r="1" spans="1:3" ht="32.1" customHeight="1">
       <c r="A1" s="51" t="s">
         <v>68</v>
       </c>
